--- a/data/annual_loads_stations.xlsx
+++ b/data/annual_loads_stations.xlsx
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8 )</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8 )</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8 )</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rud Nitelva (N8 )</t>
+          <t>Rud Nitelva (N8)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">

--- a/data/annual_loads_stations.xlsx
+++ b/data/annual_loads_stations.xlsx
@@ -471,16 +471,16 @@
         <v>1990</v>
       </c>
       <c r="C2" t="n">
-        <v>96.30059032878843</v>
+        <v>115.5607083945461</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1347203190877</v>
+        <v>3.761664382905239</v>
       </c>
       <c r="E2" t="n">
-        <v>1125.209561750275</v>
+        <v>1350.251474100329</v>
       </c>
       <c r="F2" t="n">
-        <v>374.5739838278247</v>
+        <v>449.4887805933897</v>
       </c>
     </row>
     <row r="3">
@@ -493,16 +493,16 @@
         <v>1991</v>
       </c>
       <c r="C3" t="n">
-        <v>188.7482206134084</v>
+        <v>226.4978647360902</v>
       </c>
       <c r="D3" t="n">
-        <v>8.012178567612983</v>
+        <v>9.61461428113558</v>
       </c>
       <c r="E3" t="n">
-        <v>3578.643200174778</v>
+        <v>4294.371840209736</v>
       </c>
       <c r="F3" t="n">
-        <v>520.2077944817898</v>
+        <v>624.249353378148</v>
       </c>
     </row>
     <row r="4">
@@ -515,16 +515,16 @@
         <v>1992</v>
       </c>
       <c r="C4" t="n">
-        <v>170.7536891755707</v>
+        <v>204.9044270106848</v>
       </c>
       <c r="D4" t="n">
-        <v>5.391132912906606</v>
+        <v>6.469359495487926</v>
       </c>
       <c r="E4" t="n">
-        <v>3016.063269422176</v>
+        <v>3619.275923306611</v>
       </c>
       <c r="F4" t="n">
-        <v>459.9739111821835</v>
+        <v>551.9686934186202</v>
       </c>
     </row>
     <row r="5">
@@ -537,16 +537,16 @@
         <v>1998</v>
       </c>
       <c r="C5" t="n">
-        <v>232.1505511968962</v>
+        <v>278.5806614362754</v>
       </c>
       <c r="D5" t="n">
-        <v>8.431334550740825</v>
+        <v>10.11760146088899</v>
       </c>
       <c r="E5" t="n">
-        <v>3146.030529412534</v>
+        <v>3775.236635295039</v>
       </c>
       <c r="F5" t="n">
-        <v>662.2956777503387</v>
+        <v>794.7548133004062</v>
       </c>
     </row>
     <row r="6">
@@ -559,13 +559,13 @@
         <v>1999</v>
       </c>
       <c r="C6" t="n">
-        <v>234.1475415505378</v>
+        <v>280.9770498606454</v>
       </c>
       <c r="D6" t="n">
-        <v>24.47429872815458</v>
+        <v>29.36915847378549</v>
       </c>
       <c r="E6" t="n">
-        <v>19898.39708805639</v>
+        <v>23878.07650566768</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -579,16 +579,16 @@
         <v>2000</v>
       </c>
       <c r="C7" t="n">
-        <v>266.7646031034193</v>
+        <v>320.1175237241032</v>
       </c>
       <c r="D7" t="n">
-        <v>34.21237725447871</v>
+        <v>41.05485270537446</v>
       </c>
       <c r="E7" t="n">
-        <v>24993.56610344455</v>
+        <v>29992.27932413347</v>
       </c>
       <c r="F7" t="n">
-        <v>1493.99805899891</v>
+        <v>1792.797670798693</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         <v>2001</v>
       </c>
       <c r="C8" t="n">
-        <v>154.1442611016148</v>
+        <v>184.9731133219378</v>
       </c>
       <c r="D8" t="n">
-        <v>8.572596013177359</v>
+        <v>10.28711521581283</v>
       </c>
       <c r="E8" t="n">
-        <v>5172.394504778814</v>
+        <v>6206.873405734576</v>
       </c>
       <c r="F8" t="n">
-        <v>670.826068318765</v>
+        <v>804.991281982518</v>
       </c>
     </row>
     <row r="9">
@@ -623,16 +623,16 @@
         <v>2002</v>
       </c>
       <c r="C9" t="n">
-        <v>159.1984219501458</v>
+        <v>191.038106340175</v>
       </c>
       <c r="D9" t="n">
-        <v>6.946396725855804</v>
+        <v>8.335676071026965</v>
       </c>
       <c r="E9" t="n">
-        <v>2521.484009921179</v>
+        <v>3025.780811905415</v>
       </c>
       <c r="F9" t="n">
-        <v>532.1827648935327</v>
+        <v>638.6193178722393</v>
       </c>
     </row>
     <row r="10">
@@ -645,16 +645,16 @@
         <v>2003</v>
       </c>
       <c r="C10" t="n">
-        <v>245.7961613673744</v>
+        <v>294.9553936408491</v>
       </c>
       <c r="D10" t="n">
-        <v>6.342597391154928</v>
+        <v>7.611116869385912</v>
       </c>
       <c r="E10" t="n">
-        <v>3803.393076469351</v>
+        <v>4564.071691763222</v>
       </c>
       <c r="F10" t="n">
-        <v>565.9485319268596</v>
+        <v>679.138238312231</v>
       </c>
     </row>
     <row r="11">
@@ -667,16 +667,16 @@
         <v>2004</v>
       </c>
       <c r="C11" t="n">
-        <v>263.4371918655395</v>
+        <v>316.1246302386475</v>
       </c>
       <c r="D11" t="n">
-        <v>23.66753112085047</v>
+        <v>28.40103734502056</v>
       </c>
       <c r="E11" t="n">
-        <v>8309.285390894092</v>
+        <v>9971.142469072911</v>
       </c>
       <c r="F11" t="n">
-        <v>1008.343655808091</v>
+        <v>1210.012386969709</v>
       </c>
     </row>
     <row r="12">
@@ -689,16 +689,16 @@
         <v>2005</v>
       </c>
       <c r="C12" t="n">
-        <v>128.9171406727309</v>
+        <v>154.7005688072772</v>
       </c>
       <c r="D12" t="n">
-        <v>6.468861752526793</v>
+        <v>7.762634103032152</v>
       </c>
       <c r="E12" t="n">
-        <v>3656.207449077632</v>
+        <v>4387.448938893157</v>
       </c>
       <c r="F12" t="n">
-        <v>452.3613927363837</v>
+        <v>542.8336712836602</v>
       </c>
     </row>
     <row r="13">
@@ -711,16 +711,16 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
-        <v>351.9950641189254</v>
+        <v>422.3940769427105</v>
       </c>
       <c r="D13" t="n">
-        <v>18.35656707511707</v>
+        <v>22.02788049014049</v>
       </c>
       <c r="E13" t="n">
-        <v>11023.05360549697</v>
+        <v>13227.66432659636</v>
       </c>
       <c r="F13" t="n">
-        <v>2259.156924488845</v>
+        <v>2710.988309386613</v>
       </c>
     </row>
     <row r="14">
@@ -733,16 +733,16 @@
         <v>2011</v>
       </c>
       <c r="C14" t="n">
-        <v>227.4711671423098</v>
+        <v>272.9654005707717</v>
       </c>
       <c r="D14" t="n">
-        <v>17.64044516061659</v>
+        <v>21.16853419273991</v>
       </c>
       <c r="E14" t="n">
-        <v>7263.28323896975</v>
+        <v>8715.939886763699</v>
       </c>
       <c r="F14" t="n">
-        <v>874.4832494010203</v>
+        <v>1049.379899281224</v>
       </c>
     </row>
     <row r="15">
@@ -755,16 +755,16 @@
         <v>2012</v>
       </c>
       <c r="C15" t="n">
-        <v>296.7613164281397</v>
+        <v>356.1135797137676</v>
       </c>
       <c r="D15" t="n">
-        <v>16.92799980201673</v>
+        <v>20.31359976242008</v>
       </c>
       <c r="E15" t="n">
-        <v>4552.484347226173</v>
+        <v>5462.981216671406</v>
       </c>
       <c r="F15" t="n">
-        <v>858.8718271660003</v>
+        <v>1030.6461925992</v>
       </c>
     </row>
     <row r="16">
@@ -777,16 +777,16 @@
         <v>2017</v>
       </c>
       <c r="C16" t="n">
-        <v>154.5885724551667</v>
+        <v>185.5062869462001</v>
       </c>
       <c r="D16" t="n">
-        <v>18.58664680309908</v>
+        <v>22.30397616371891</v>
       </c>
       <c r="E16" t="n">
-        <v>10188.07958802054</v>
+        <v>12225.69550562465</v>
       </c>
       <c r="F16" t="n">
-        <v>1028.580819360197</v>
+        <v>1234.296983232236</v>
       </c>
     </row>
     <row r="17">
@@ -799,16 +799,16 @@
         <v>2018</v>
       </c>
       <c r="C17" t="n">
-        <v>186.822721143284</v>
+        <v>224.1872653719408</v>
       </c>
       <c r="D17" t="n">
-        <v>4.94567136354902</v>
+        <v>5.934805636258826</v>
       </c>
       <c r="E17" t="n">
-        <v>2491.758165784657</v>
+        <v>2990.109798941589</v>
       </c>
       <c r="F17" t="n">
-        <v>884.3723361234939</v>
+        <v>1061.246803348193</v>
       </c>
     </row>
     <row r="18">
@@ -821,16 +821,16 @@
         <v>2019</v>
       </c>
       <c r="C18" t="n">
-        <v>440.5014258825511</v>
+        <v>528.6017110590611</v>
       </c>
       <c r="D18" t="n">
-        <v>14.04145849319338</v>
+        <v>16.84975019183205</v>
       </c>
       <c r="E18" t="n">
-        <v>8125.673825444294</v>
+        <v>9750.808590533152</v>
       </c>
       <c r="F18" t="n">
-        <v>1260.966183742439</v>
+        <v>1513.159420490927</v>
       </c>
     </row>
     <row r="19">
@@ -843,16 +843,16 @@
         <v>2020</v>
       </c>
       <c r="C19" t="n">
-        <v>291.2052329111322</v>
+        <v>349.4462794933586</v>
       </c>
       <c r="D19" t="n">
-        <v>30.82973448211412</v>
+        <v>36.99568137853694</v>
       </c>
       <c r="E19" t="n">
-        <v>14231.5191352893</v>
+        <v>17077.82296234715</v>
       </c>
       <c r="F19" t="n">
-        <v>1785.417748541472</v>
+        <v>2142.501298249766</v>
       </c>
     </row>
     <row r="20">
@@ -865,16 +865,16 @@
         <v>2021</v>
       </c>
       <c r="C20" t="n">
-        <v>221.6256685090861</v>
+        <v>265.9508022109033</v>
       </c>
       <c r="D20" t="n">
-        <v>18.0039315317244</v>
+        <v>21.60471783806928</v>
       </c>
       <c r="E20" t="n">
-        <v>15541.56851240802</v>
+        <v>18649.88221488962</v>
       </c>
       <c r="F20" t="n">
-        <v>874.4143508789429</v>
+        <v>1049.297221054731</v>
       </c>
     </row>
     <row r="21">
@@ -887,16 +887,16 @@
         <v>2022</v>
       </c>
       <c r="C21" t="n">
-        <v>107.1003143888254</v>
+        <v>128.5203772665904</v>
       </c>
       <c r="D21" t="n">
-        <v>3.598717843628056</v>
+        <v>4.318461412353668</v>
       </c>
       <c r="E21" t="n">
-        <v>1770.888860789331</v>
+        <v>2125.066632947197</v>
       </c>
       <c r="F21" t="n">
-        <v>474.8909789615805</v>
+        <v>569.8691747538966</v>
       </c>
     </row>
     <row r="22">
@@ -909,16 +909,16 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>233.5307305727482</v>
+        <v>280.2368766872979</v>
       </c>
       <c r="D22" t="n">
-        <v>22.75925785361399</v>
+        <v>27.3111094243368</v>
       </c>
       <c r="E22" t="n">
-        <v>18988.4210282388</v>
+        <v>22786.10523388657</v>
       </c>
       <c r="F22" t="n">
-        <v>1479.017343240393</v>
+        <v>1774.820811888472</v>
       </c>
     </row>
     <row r="23">
@@ -931,16 +931,16 @@
         <v>2024</v>
       </c>
       <c r="C23" t="n">
-        <v>199.4493896237228</v>
+        <v>239.3392675484675</v>
       </c>
       <c r="D23" t="n">
-        <v>24.74400715250938</v>
+        <v>29.69280858301125</v>
       </c>
       <c r="E23" t="n">
-        <v>21613.74679236217</v>
+        <v>25936.49615083462</v>
       </c>
       <c r="F23" t="n">
-        <v>781.2543243186807</v>
+        <v>937.5051891824171</v>
       </c>
     </row>
     <row r="24">
@@ -953,10 +953,10 @@
         <v>1981</v>
       </c>
       <c r="C24" t="n">
-        <v>304.3931151175428</v>
+        <v>365.2717381410512</v>
       </c>
       <c r="D24" t="n">
-        <v>55.4049402413238</v>
+        <v>66.48592828958857</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -971,13 +971,13 @@
         <v>1982</v>
       </c>
       <c r="C25" t="n">
-        <v>275.5828577526214</v>
+        <v>330.6994293031456</v>
       </c>
       <c r="D25" t="n">
-        <v>66.18198513378591</v>
+        <v>79.41838216054308</v>
       </c>
       <c r="E25" t="n">
-        <v>59513.55322064435</v>
+        <v>71416.26386477319</v>
       </c>
       <c r="F25" t="inlineStr"/>
     </row>
@@ -991,16 +991,16 @@
         <v>1998</v>
       </c>
       <c r="C26" t="n">
-        <v>649.4074521318513</v>
+        <v>779.2889425582216</v>
       </c>
       <c r="D26" t="n">
-        <v>27.84653404078419</v>
+        <v>33.41584084894103</v>
       </c>
       <c r="E26" t="n">
-        <v>21724.38278557832</v>
+        <v>26069.25934269399</v>
       </c>
       <c r="F26" t="n">
-        <v>1986.779373788734</v>
+        <v>2384.135248546481</v>
       </c>
     </row>
     <row r="27">
@@ -1013,16 +1013,16 @@
         <v>1999</v>
       </c>
       <c r="C27" t="n">
-        <v>484.3612244499803</v>
+        <v>581.2334693399764</v>
       </c>
       <c r="D27" t="n">
-        <v>54.22950494424273</v>
+        <v>65.07540593309129</v>
       </c>
       <c r="E27" t="n">
-        <v>42167.27407443031</v>
+        <v>50600.72888931636</v>
       </c>
       <c r="F27" t="n">
-        <v>2259.896743304323</v>
+        <v>2711.876091965187</v>
       </c>
     </row>
     <row r="28">
@@ -1035,13 +1035,13 @@
         <v>2000</v>
       </c>
       <c r="C28" t="n">
-        <v>690.0435002378422</v>
+        <v>828.0522002854108</v>
       </c>
       <c r="D28" t="n">
-        <v>134.6646046714752</v>
+        <v>161.5975256057702</v>
       </c>
       <c r="E28" t="n">
-        <v>114044.6981387203</v>
+        <v>136853.6377664644</v>
       </c>
       <c r="F28" t="inlineStr"/>
     </row>
@@ -1055,7 +1055,7 @@
         <v>2001</v>
       </c>
       <c r="C29" t="n">
-        <v>451.8774696516983</v>
+        <v>542.2529635820381</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -1071,16 +1071,16 @@
         <v>2003</v>
       </c>
       <c r="C30" t="n">
-        <v>588.0561213410042</v>
+        <v>705.6673456092049</v>
       </c>
       <c r="D30" t="n">
-        <v>39.02302914865784</v>
+        <v>46.8276349783894</v>
       </c>
       <c r="E30" t="n">
-        <v>36589.12814674148</v>
+        <v>43906.95377608976</v>
       </c>
       <c r="F30" t="n">
-        <v>1727.901807126871</v>
+        <v>2073.482168552245</v>
       </c>
     </row>
     <row r="31">
@@ -1093,13 +1093,13 @@
         <v>2004</v>
       </c>
       <c r="C31" t="n">
-        <v>342.0793504763114</v>
+        <v>410.4952205715738</v>
       </c>
       <c r="D31" t="n">
-        <v>15.79151089924417</v>
+        <v>18.94981307909301</v>
       </c>
       <c r="E31" t="n">
-        <v>10588.00816957248</v>
+        <v>12705.60980348698</v>
       </c>
       <c r="F31" t="inlineStr"/>
     </row>
@@ -1113,16 +1113,16 @@
         <v>2005</v>
       </c>
       <c r="C32" t="n">
-        <v>280.32847247463</v>
+        <v>336.394166969556</v>
       </c>
       <c r="D32" t="n">
-        <v>15.97523142240977</v>
+        <v>19.17027770689172</v>
       </c>
       <c r="E32" t="n">
-        <v>9932.859104135176</v>
+        <v>11919.43092496221</v>
       </c>
       <c r="F32" t="n">
-        <v>1137.20715868368</v>
+        <v>1364.648590420416</v>
       </c>
     </row>
     <row r="33">
@@ -1135,12 +1135,12 @@
         <v>2006</v>
       </c>
       <c r="C33" t="n">
-        <v>783.8190412426378</v>
+        <v>940.5828494911653</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>4059.042881580753</v>
+        <v>4870.851457896904</v>
       </c>
     </row>
     <row r="34">
@@ -1153,16 +1153,16 @@
         <v>2008</v>
       </c>
       <c r="C34" t="n">
-        <v>478.6091948693121</v>
+        <v>574.3310338431747</v>
       </c>
       <c r="D34" t="n">
-        <v>117.1370979963853</v>
+        <v>140.5645175956624</v>
       </c>
       <c r="E34" t="n">
-        <v>84310.08667937902</v>
+        <v>101172.1040152548</v>
       </c>
       <c r="F34" t="n">
-        <v>2070.592161131085</v>
+        <v>2484.710593357302</v>
       </c>
     </row>
     <row r="35">
@@ -1175,10 +1175,10 @@
         <v>2009</v>
       </c>
       <c r="C35" t="n">
-        <v>348.3479971826472</v>
+        <v>418.0175966191766</v>
       </c>
       <c r="D35" t="n">
-        <v>40.11242668821741</v>
+        <v>48.13491202586088</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -1193,10 +1193,10 @@
         <v>2010</v>
       </c>
       <c r="C36" t="n">
-        <v>338.7661545014682</v>
+        <v>406.519385401762</v>
       </c>
       <c r="D36" t="n">
-        <v>27.43502139705335</v>
+        <v>32.92202567646402</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1211,16 +1211,16 @@
         <v>2011</v>
       </c>
       <c r="C37" t="n">
-        <v>823.5980301748485</v>
+        <v>988.317636209818</v>
       </c>
       <c r="D37" t="n">
-        <v>95.19609917467366</v>
+        <v>114.2353190096084</v>
       </c>
       <c r="E37" t="n">
-        <v>82063.64732273221</v>
+        <v>98476.37678727867</v>
       </c>
       <c r="F37" t="n">
-        <v>2392.203079981792</v>
+        <v>2870.643695978151</v>
       </c>
     </row>
     <row r="38">
@@ -1233,16 +1233,16 @@
         <v>2012</v>
       </c>
       <c r="C38" t="n">
-        <v>545.128525654388</v>
+        <v>654.1542307852657</v>
       </c>
       <c r="D38" t="n">
-        <v>46.02699260592354</v>
+        <v>55.23239112710823</v>
       </c>
       <c r="E38" t="n">
-        <v>34668.68171266491</v>
+        <v>41602.41805519789</v>
       </c>
       <c r="F38" t="n">
-        <v>2397.845699642041</v>
+        <v>2877.414839570449</v>
       </c>
     </row>
     <row r="39">
@@ -1255,16 +1255,16 @@
         <v>2013</v>
       </c>
       <c r="C39" t="n">
-        <v>450.5991420821111</v>
+        <v>540.7189704985332</v>
       </c>
       <c r="D39" t="n">
-        <v>67.16227407043274</v>
+        <v>80.59472888451928</v>
       </c>
       <c r="E39" t="n">
-        <v>62391.93407737749</v>
+        <v>74870.32089285302</v>
       </c>
       <c r="F39" t="n">
-        <v>2307.952215104257</v>
+        <v>2769.542658125109</v>
       </c>
     </row>
     <row r="40">
@@ -1277,16 +1277,16 @@
         <v>2014</v>
       </c>
       <c r="C40" t="n">
-        <v>505.3150230049128</v>
+        <v>606.3780276058955</v>
       </c>
       <c r="D40" t="n">
-        <v>71.99756927116744</v>
+        <v>86.39708312540093</v>
       </c>
       <c r="E40" t="n">
-        <v>36857.55786871876</v>
+        <v>44229.06944246251</v>
       </c>
       <c r="F40" t="n">
-        <v>3763.989929462228</v>
+        <v>4516.787915354675</v>
       </c>
     </row>
     <row r="41">
@@ -1299,16 +1299,16 @@
         <v>2015</v>
       </c>
       <c r="C41" t="n">
-        <v>607.4243542138613</v>
+        <v>728.9092250566333</v>
       </c>
       <c r="D41" t="n">
-        <v>35.04509354537427</v>
+        <v>42.05411225444912</v>
       </c>
       <c r="E41" t="n">
-        <v>26811.97535525506</v>
+        <v>32174.37042630606</v>
       </c>
       <c r="F41" t="n">
-        <v>3163.581348996943</v>
+        <v>3796.297618796331</v>
       </c>
     </row>
     <row r="42">
@@ -1321,13 +1321,13 @@
         <v>2016</v>
       </c>
       <c r="C42" t="n">
-        <v>615.858221701498</v>
+        <v>739.0298660417974</v>
       </c>
       <c r="D42" t="n">
-        <v>47.77177309769189</v>
+        <v>57.32612771723028</v>
       </c>
       <c r="E42" t="n">
-        <v>67230.24354153419</v>
+        <v>80676.29224984105</v>
       </c>
       <c r="F42" t="inlineStr"/>
     </row>
@@ -1341,16 +1341,16 @@
         <v>2017</v>
       </c>
       <c r="C43" t="n">
-        <v>416.7407238762134</v>
+        <v>500.0888686514559</v>
       </c>
       <c r="D43" t="n">
-        <v>25.71107161791929</v>
+        <v>30.85328594150314</v>
       </c>
       <c r="E43" t="n">
-        <v>11783.8372365933</v>
+        <v>14140.60468391196</v>
       </c>
       <c r="F43" t="n">
-        <v>2516.403929879331</v>
+        <v>3019.684715855197</v>
       </c>
     </row>
     <row r="44">
@@ -1363,16 +1363,16 @@
         <v>2018</v>
       </c>
       <c r="C44" t="n">
-        <v>551.7087044692302</v>
+        <v>662.0504453630762</v>
       </c>
       <c r="D44" t="n">
-        <v>41.19732365073493</v>
+        <v>49.43678838088191</v>
       </c>
       <c r="E44" t="n">
-        <v>33922.50702079462</v>
+        <v>40707.00842495356</v>
       </c>
       <c r="F44" t="n">
-        <v>2348.908564763011</v>
+        <v>2818.690277715614</v>
       </c>
     </row>
     <row r="45">
@@ -1385,16 +1385,16 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>674.4083968582661</v>
+        <v>809.2900762299192</v>
       </c>
       <c r="D45" t="n">
-        <v>41.12402941077661</v>
+        <v>49.34883529293193</v>
       </c>
       <c r="E45" t="n">
-        <v>28212.18336455369</v>
+        <v>33854.62003746442</v>
       </c>
       <c r="F45" t="n">
-        <v>2768.114740735377</v>
+        <v>3321.737688882451</v>
       </c>
     </row>
     <row r="46">
@@ -1407,16 +1407,16 @@
         <v>2020</v>
       </c>
       <c r="C46" t="n">
-        <v>677.2499128151371</v>
+        <v>812.6998953781645</v>
       </c>
       <c r="D46" t="n">
-        <v>44.11151944672378</v>
+        <v>52.93382333606854</v>
       </c>
       <c r="E46" t="n">
-        <v>27165.17768415949</v>
+        <v>32598.21322099139</v>
       </c>
       <c r="F46" t="n">
-        <v>3975.932822056403</v>
+        <v>4771.119386467683</v>
       </c>
     </row>
     <row r="47">
@@ -1429,16 +1429,16 @@
         <v>2021</v>
       </c>
       <c r="C47" t="n">
-        <v>440.3044834091844</v>
+        <v>528.3653800910212</v>
       </c>
       <c r="D47" t="n">
-        <v>27.6561364762565</v>
+        <v>33.1873637715078</v>
       </c>
       <c r="E47" t="n">
-        <v>20371.84295442859</v>
+        <v>24446.2115453143</v>
       </c>
       <c r="F47" t="n">
-        <v>2496.01762952636</v>
+        <v>2995.221155431632</v>
       </c>
     </row>
     <row r="48">
@@ -1451,16 +1451,16 @@
         <v>2022</v>
       </c>
       <c r="C48" t="n">
-        <v>282.3011334795617</v>
+        <v>338.7613601754741</v>
       </c>
       <c r="D48" t="n">
-        <v>15.39393247427772</v>
+        <v>18.47271896913326</v>
       </c>
       <c r="E48" t="n">
-        <v>10955.20040571225</v>
+        <v>13146.2404868547</v>
       </c>
       <c r="F48" t="n">
-        <v>1607.848021315618</v>
+        <v>1929.417625578742</v>
       </c>
     </row>
     <row r="49">
@@ -1473,13 +1473,13 @@
         <v>2023</v>
       </c>
       <c r="C49" t="n">
-        <v>943.4738291615109</v>
+        <v>1132.168594993813</v>
       </c>
       <c r="D49" t="n">
-        <v>156.5137961295465</v>
+        <v>187.8165553554557</v>
       </c>
       <c r="E49" t="n">
-        <v>159695.98533989</v>
+        <v>191635.182407868</v>
       </c>
       <c r="F49" t="inlineStr"/>
     </row>
@@ -1493,16 +1493,16 @@
         <v>2024</v>
       </c>
       <c r="C50" t="n">
-        <v>622.9263856050876</v>
+        <v>747.5116627261049</v>
       </c>
       <c r="D50" t="n">
-        <v>104.8708335191818</v>
+        <v>125.8450002230182</v>
       </c>
       <c r="E50" t="n">
-        <v>82877.09298399382</v>
+        <v>99452.51158079253</v>
       </c>
       <c r="F50" t="n">
-        <v>4490.266514474061</v>
+        <v>5388.319817368871</v>
       </c>
     </row>
     <row r="51">
@@ -1515,16 +1515,16 @@
         <v>1995</v>
       </c>
       <c r="C51" t="n">
-        <v>180.4314967042461</v>
+        <v>216.5177960450953</v>
       </c>
       <c r="D51" t="n">
-        <v>5.516328336874922</v>
+        <v>6.619594004249908</v>
       </c>
       <c r="E51" t="n">
-        <v>2650.120471453714</v>
+        <v>3180.144565744456</v>
       </c>
       <c r="F51" t="n">
-        <v>790.5269613016925</v>
+        <v>948.6323535620309</v>
       </c>
     </row>
     <row r="52">
@@ -1537,16 +1537,16 @@
         <v>1996</v>
       </c>
       <c r="C52" t="n">
-        <v>170.9556968645851</v>
+        <v>205.1468362375021</v>
       </c>
       <c r="D52" t="n">
-        <v>5.736364486791113</v>
+        <v>6.883637384149339</v>
       </c>
       <c r="E52" t="n">
-        <v>2468.757063908087</v>
+        <v>2962.508476689706</v>
       </c>
       <c r="F52" t="n">
-        <v>563.9077960409389</v>
+        <v>676.6893552491267</v>
       </c>
     </row>
     <row r="53">
@@ -1559,16 +1559,16 @@
         <v>1997</v>
       </c>
       <c r="C53" t="n">
-        <v>163.6134316039648</v>
+        <v>196.3361179247576</v>
       </c>
       <c r="D53" t="n">
-        <v>4.936390257601038</v>
+        <v>5.923668309121244</v>
       </c>
       <c r="E53" t="n">
-        <v>2284.706768465875</v>
+        <v>2741.648122159049</v>
       </c>
       <c r="F53" t="n">
-        <v>589.6810521024084</v>
+        <v>707.6172625228901</v>
       </c>
     </row>
     <row r="54">
@@ -1581,16 +1581,16 @@
         <v>1998</v>
       </c>
       <c r="C54" t="n">
-        <v>188.6341568660245</v>
+        <v>226.3609882392294</v>
       </c>
       <c r="D54" t="n">
-        <v>9.713960797046463</v>
+        <v>11.65675295645575</v>
       </c>
       <c r="E54" t="n">
-        <v>4090.003102208354</v>
+        <v>4908.003722650024</v>
       </c>
       <c r="F54" t="n">
-        <v>839.6614167156348</v>
+        <v>1007.593700058762</v>
       </c>
     </row>
     <row r="55">
@@ -1603,16 +1603,16 @@
         <v>1999</v>
       </c>
       <c r="C55" t="n">
-        <v>192.4620193807922</v>
+        <v>230.9544232569506</v>
       </c>
       <c r="D55" t="n">
-        <v>6.84246607639504</v>
+        <v>8.210959291674046</v>
       </c>
       <c r="E55" t="n">
-        <v>2613.428988798242</v>
+        <v>3136.114786557891</v>
       </c>
       <c r="F55" t="n">
-        <v>1016.332312623378</v>
+        <v>1219.598775148054</v>
       </c>
     </row>
     <row r="56">
@@ -1625,16 +1625,16 @@
         <v>2000</v>
       </c>
       <c r="C56" t="n">
-        <v>284.2772995650715</v>
+        <v>341.1327594780858</v>
       </c>
       <c r="D56" t="n">
-        <v>17.41479512414809</v>
+        <v>20.8977541489777</v>
       </c>
       <c r="E56" t="n">
-        <v>8448.882654692557</v>
+        <v>10138.65918563107</v>
       </c>
       <c r="F56" t="n">
-        <v>1771.792922183727</v>
+        <v>2126.151506620473</v>
       </c>
     </row>
     <row r="57">
@@ -1647,16 +1647,16 @@
         <v>2001</v>
       </c>
       <c r="C57" t="n">
-        <v>193.8833114147672</v>
+        <v>232.6599736977205</v>
       </c>
       <c r="D57" t="n">
-        <v>7.109410452428713</v>
+        <v>8.531292542914452</v>
       </c>
       <c r="E57" t="n">
-        <v>3352.332461804814</v>
+        <v>4022.798954165779</v>
       </c>
       <c r="F57" t="n">
-        <v>814.3077196415743</v>
+        <v>977.1692635698893</v>
       </c>
     </row>
     <row r="58">
@@ -1669,16 +1669,16 @@
         <v>2002</v>
       </c>
       <c r="C58" t="n">
-        <v>161.2352507217024</v>
+        <v>193.4823008660429</v>
       </c>
       <c r="D58" t="n">
-        <v>4.983358232744824</v>
+        <v>5.980029879293789</v>
       </c>
       <c r="E58" t="n">
-        <v>1285.122202374108</v>
+        <v>1542.14664284893</v>
       </c>
       <c r="F58" t="n">
-        <v>669.9605676200343</v>
+        <v>803.9526811440414</v>
       </c>
     </row>
     <row r="59">
@@ -1691,16 +1691,16 @@
         <v>2003</v>
       </c>
       <c r="C59" t="n">
-        <v>192.3993909227359</v>
+        <v>230.8792691072831</v>
       </c>
       <c r="D59" t="n">
-        <v>3.115055555035486</v>
+        <v>3.738066666042583</v>
       </c>
       <c r="E59" t="n">
-        <v>972.0282018243046</v>
+        <v>1166.433842189165</v>
       </c>
       <c r="F59" t="n">
-        <v>687.2916693523126</v>
+        <v>824.7500032227753</v>
       </c>
     </row>
     <row r="60">
@@ -1713,16 +1713,16 @@
         <v>2004</v>
       </c>
       <c r="C60" t="n">
-        <v>237.1366923449895</v>
+        <v>284.5640308139873</v>
       </c>
       <c r="D60" t="n">
-        <v>5.653334046425802</v>
+        <v>6.784000855710963</v>
       </c>
       <c r="E60" t="n">
-        <v>1235.49053565691</v>
+        <v>1482.588642788291</v>
       </c>
       <c r="F60" t="n">
-        <v>821.1102160316318</v>
+        <v>985.3322592379582</v>
       </c>
     </row>
     <row r="61">
@@ -1735,16 +1735,16 @@
         <v>2005</v>
       </c>
       <c r="C61" t="n">
-        <v>218.5500044102283</v>
+        <v>262.2600052922739</v>
       </c>
       <c r="D61" t="n">
-        <v>4.804747530895016</v>
+        <v>5.765697037074019</v>
       </c>
       <c r="E61" t="n">
-        <v>1595.628360539181</v>
+        <v>1914.754032647017</v>
       </c>
       <c r="F61" t="n">
-        <v>675.972945909862</v>
+        <v>811.1675350918348</v>
       </c>
     </row>
     <row r="62">
@@ -1757,16 +1757,16 @@
         <v>2006</v>
       </c>
       <c r="C62" t="n">
-        <v>217.1084860908804</v>
+        <v>260.5301833090566</v>
       </c>
       <c r="D62" t="n">
-        <v>6.982059543591169</v>
+        <v>8.378471452309405</v>
       </c>
       <c r="E62" t="n">
-        <v>2280.732685875446</v>
+        <v>2736.879223050535</v>
       </c>
       <c r="F62" t="n">
-        <v>1036.069394688994</v>
+        <v>1243.283273626793</v>
       </c>
     </row>
     <row r="63">
@@ -1779,16 +1779,16 @@
         <v>2008</v>
       </c>
       <c r="C63" t="n">
-        <v>222.0315509319277</v>
+        <v>266.4378611183134</v>
       </c>
       <c r="D63" t="n">
-        <v>10.93659231223443</v>
+        <v>13.12391077468133</v>
       </c>
       <c r="E63" t="n">
-        <v>3258.99245708754</v>
+        <v>3910.79094850505</v>
       </c>
       <c r="F63" t="n">
-        <v>1125.292877374202</v>
+        <v>1350.351452849043</v>
       </c>
     </row>
     <row r="64">
@@ -1801,16 +1801,16 @@
         <v>2010</v>
       </c>
       <c r="C64" t="n">
-        <v>157.2841141259825</v>
+        <v>188.740936951179</v>
       </c>
       <c r="D64" t="n">
-        <v>4.00844045605811</v>
+        <v>4.810128547269732</v>
       </c>
       <c r="E64" t="n">
-        <v>1703.133457570276</v>
+        <v>2043.760149084331</v>
       </c>
       <c r="F64" t="n">
-        <v>688.8097618249457</v>
+        <v>826.5717141899352</v>
       </c>
     </row>
     <row r="65">
@@ -1823,16 +1823,16 @@
         <v>2011</v>
       </c>
       <c r="C65" t="n">
-        <v>213.9472057180424</v>
+        <v>256.7366468616509</v>
       </c>
       <c r="D65" t="n">
-        <v>15.45802703577046</v>
+        <v>18.54963244292455</v>
       </c>
       <c r="E65" t="n">
-        <v>8774.090486162861</v>
+        <v>10528.90858339543</v>
       </c>
       <c r="F65" t="n">
-        <v>1235.295489166398</v>
+        <v>1482.354586999677</v>
       </c>
     </row>
     <row r="66">
@@ -1845,16 +1845,16 @@
         <v>2012</v>
       </c>
       <c r="C66" t="n">
-        <v>233.9367085822666</v>
+        <v>280.7240502987199</v>
       </c>
       <c r="D66" t="n">
-        <v>8.181047247073964</v>
+        <v>9.817256696488759</v>
       </c>
       <c r="E66" t="n">
-        <v>4433.939076850127</v>
+        <v>5320.726892220153</v>
       </c>
       <c r="F66" t="n">
-        <v>1114.584913235378</v>
+        <v>1337.501895882453</v>
       </c>
     </row>
     <row r="67">
@@ -1867,16 +1867,16 @@
         <v>2013</v>
       </c>
       <c r="C67" t="n">
-        <v>232.9255573583919</v>
+        <v>279.5106688300704</v>
       </c>
       <c r="D67" t="n">
-        <v>16.34694951765403</v>
+        <v>19.61633942118484</v>
       </c>
       <c r="E67" t="n">
-        <v>7960.863773878839</v>
+        <v>9553.036528654606</v>
       </c>
       <c r="F67" t="n">
-        <v>1140.953826967866</v>
+        <v>1369.144592361439</v>
       </c>
     </row>
     <row r="68">
@@ -1889,16 +1889,16 @@
         <v>2015</v>
       </c>
       <c r="C68" t="n">
-        <v>234.4931513848367</v>
+        <v>281.391781661804</v>
       </c>
       <c r="D68" t="n">
-        <v>5.766342812605111</v>
+        <v>6.919611375126133</v>
       </c>
       <c r="E68" t="n">
-        <v>2633.375374607484</v>
+        <v>3160.05044952898</v>
       </c>
       <c r="F68" t="n">
-        <v>1512.163390309604</v>
+        <v>1814.596068371525</v>
       </c>
     </row>
     <row r="69">
@@ -1911,16 +1911,16 @@
         <v>2016</v>
       </c>
       <c r="C69" t="n">
-        <v>161.3116124990245</v>
+        <v>193.5739349988294</v>
       </c>
       <c r="D69" t="n">
-        <v>3.846472470387216</v>
+        <v>4.615766964464658</v>
       </c>
       <c r="E69" t="n">
-        <v>1764.971769693095</v>
+        <v>2117.966123631714</v>
       </c>
       <c r="F69" t="n">
-        <v>974.3795113056947</v>
+        <v>1169.255413566833</v>
       </c>
     </row>
     <row r="70">
@@ -1933,13 +1933,13 @@
         <v>2017</v>
       </c>
       <c r="C70" t="n">
-        <v>215.0588328286262</v>
+        <v>258.0705993943514</v>
       </c>
       <c r="D70" t="n">
-        <v>5.563446677467931</v>
+        <v>6.676136012961517</v>
       </c>
       <c r="E70" t="n">
-        <v>2130.413732762145</v>
+        <v>2556.496479314575</v>
       </c>
       <c r="F70" t="inlineStr"/>
     </row>
@@ -1953,13 +1953,13 @@
         <v>2018</v>
       </c>
       <c r="C71" t="n">
-        <v>259.8255848372802</v>
+        <v>311.7907018047362</v>
       </c>
       <c r="D71" t="n">
-        <v>9.656308156726903</v>
+        <v>11.58756978807228</v>
       </c>
       <c r="E71" t="n">
-        <v>5011.483488395169</v>
+        <v>6013.780186074205</v>
       </c>
       <c r="F71" t="inlineStr"/>
     </row>
@@ -1973,13 +1973,13 @@
         <v>2020</v>
       </c>
       <c r="C72" t="n">
-        <v>288.9326569669736</v>
+        <v>346.7191883603683</v>
       </c>
       <c r="D72" t="n">
-        <v>19.19477555959745</v>
+        <v>23.03373067151695</v>
       </c>
       <c r="E72" t="n">
-        <v>8535.723962733004</v>
+        <v>10242.86875527961</v>
       </c>
       <c r="F72" t="inlineStr"/>
     </row>
@@ -1993,16 +1993,16 @@
         <v>2023</v>
       </c>
       <c r="C73" t="n">
-        <v>261.000084105064</v>
+        <v>313.2001009260769</v>
       </c>
       <c r="D73" t="n">
-        <v>7.126130104485717</v>
+        <v>8.551356125382863</v>
       </c>
       <c r="E73" t="n">
-        <v>1502.728685943116</v>
+        <v>1803.274423131739</v>
       </c>
       <c r="F73" t="n">
-        <v>2370.4529407419</v>
+        <v>2844.543528890281</v>
       </c>
     </row>
     <row r="74">
@@ -2015,16 +2015,16 @@
         <v>2024</v>
       </c>
       <c r="C74" t="n">
-        <v>257.6686272076719</v>
+        <v>309.2023526492062</v>
       </c>
       <c r="D74" t="n">
-        <v>6.76079145494283</v>
+        <v>8.112949745931397</v>
       </c>
       <c r="E74" t="n">
-        <v>3782.439507361999</v>
+        <v>4538.9274088344</v>
       </c>
       <c r="F74" t="n">
-        <v>2243.405118186943</v>
+        <v>2692.086141824332</v>
       </c>
     </row>
     <row r="75">
@@ -2037,16 +2037,16 @@
         <v>1998</v>
       </c>
       <c r="C75" t="n">
-        <v>426.4816001632614</v>
+        <v>511.7779201959133</v>
       </c>
       <c r="D75" t="n">
-        <v>30.16251303447313</v>
+        <v>36.19501564136775</v>
       </c>
       <c r="E75" t="n">
-        <v>26068.37996974645</v>
+        <v>31282.05596369573</v>
       </c>
       <c r="F75" t="n">
-        <v>1936.952119743586</v>
+        <v>2324.342543692302</v>
       </c>
     </row>
     <row r="76">
@@ -2059,16 +2059,16 @@
         <v>1999</v>
       </c>
       <c r="C76" t="n">
-        <v>393.9353773799915</v>
+        <v>472.7224528559897</v>
       </c>
       <c r="D76" t="n">
-        <v>40.42414343170317</v>
+        <v>48.50897211804379</v>
       </c>
       <c r="E76" t="n">
-        <v>35055.5279837655</v>
+        <v>42066.63358051859</v>
       </c>
       <c r="F76" t="n">
-        <v>2492.625469429364</v>
+        <v>2991.150563315237</v>
       </c>
     </row>
     <row r="77">
@@ -2081,13 +2081,13 @@
         <v>2000</v>
       </c>
       <c r="C77" t="n">
-        <v>548.3931053140336</v>
+        <v>658.0717263768403</v>
       </c>
       <c r="D77" t="n">
-        <v>116.9241592692605</v>
+        <v>140.3089911231126</v>
       </c>
       <c r="E77" t="n">
-        <v>97807.33058148384</v>
+        <v>117368.7966977806</v>
       </c>
       <c r="F77" t="inlineStr"/>
     </row>
@@ -2101,13 +2101,13 @@
         <v>2001</v>
       </c>
       <c r="C78" t="n">
-        <v>276.2398101001585</v>
+        <v>331.4877721201903</v>
       </c>
       <c r="D78" t="n">
-        <v>28.79415088558074</v>
+        <v>34.55298106269688</v>
       </c>
       <c r="E78" t="n">
-        <v>19370.08117636229</v>
+        <v>23244.09741163474</v>
       </c>
       <c r="F78" t="inlineStr"/>
     </row>
@@ -2121,13 +2121,13 @@
         <v>2002</v>
       </c>
       <c r="C79" t="n">
-        <v>245.4512809702148</v>
+        <v>294.5415371642576</v>
       </c>
       <c r="D79" t="n">
-        <v>24.28832069354698</v>
+        <v>29.14598483225638</v>
       </c>
       <c r="E79" t="n">
-        <v>18535.31047067908</v>
+        <v>22242.37256481489</v>
       </c>
       <c r="F79" t="inlineStr"/>
     </row>
@@ -2141,13 +2141,13 @@
         <v>2004</v>
       </c>
       <c r="C80" t="n">
-        <v>421.9010650993958</v>
+        <v>506.2812781192748</v>
       </c>
       <c r="D80" t="n">
-        <v>31.24742123431617</v>
+        <v>37.49690548117942</v>
       </c>
       <c r="E80" t="n">
-        <v>28517.81547510984</v>
+        <v>34221.37857013181</v>
       </c>
       <c r="F80" t="inlineStr"/>
     </row>
@@ -2161,13 +2161,13 @@
         <v>2005</v>
       </c>
       <c r="C81" t="n">
-        <v>263.9847842404588</v>
+        <v>316.7817410885504</v>
       </c>
       <c r="D81" t="n">
-        <v>21.09103636834309</v>
+        <v>25.30924364201172</v>
       </c>
       <c r="E81" t="n">
-        <v>15587.2549213544</v>
+        <v>18704.70590562527</v>
       </c>
       <c r="F81" t="inlineStr"/>
     </row>
@@ -2181,13 +2181,13 @@
         <v>2006</v>
       </c>
       <c r="C82" t="n">
-        <v>618.8049837241857</v>
+        <v>742.5659804690229</v>
       </c>
       <c r="D82" t="n">
-        <v>32.48407852310669</v>
+        <v>38.98089422772803</v>
       </c>
       <c r="E82" t="n">
-        <v>31878.28730718934</v>
+        <v>38253.94476862722</v>
       </c>
       <c r="F82" t="inlineStr"/>
     </row>
@@ -2201,10 +2201,10 @@
         <v>1980</v>
       </c>
       <c r="C83" t="n">
-        <v>421.2650805049176</v>
+        <v>505.5180966059012</v>
       </c>
       <c r="D83" t="n">
-        <v>17.63146062382478</v>
+        <v>21.15775274858974</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -2219,16 +2219,16 @@
         <v>1981</v>
       </c>
       <c r="C84" t="n">
-        <v>458.6465405227242</v>
+        <v>550.3758486272691</v>
       </c>
       <c r="D84" t="n">
-        <v>29.11217028896905</v>
+        <v>34.93460434676286</v>
       </c>
       <c r="E84" t="n">
-        <v>4693.772018170561</v>
+        <v>5632.526421804672</v>
       </c>
       <c r="F84" t="n">
-        <v>1018.956404069343</v>
+        <v>1222.747684883211</v>
       </c>
     </row>
     <row r="85">
@@ -2241,16 +2241,16 @@
         <v>1982</v>
       </c>
       <c r="C85" t="n">
-        <v>308.7930052271803</v>
+        <v>370.5516062726167</v>
       </c>
       <c r="D85" t="n">
-        <v>19.08936452912569</v>
+        <v>22.90723743495083</v>
       </c>
       <c r="E85" t="n">
-        <v>4139.203127452935</v>
+        <v>4967.043752943522</v>
       </c>
       <c r="F85" t="n">
-        <v>1223.942126596877</v>
+        <v>1468.730551916253</v>
       </c>
     </row>
     <row r="86">
@@ -2263,13 +2263,13 @@
         <v>1983</v>
       </c>
       <c r="C86" t="n">
-        <v>541.5424996070044</v>
+        <v>649.8509995284052</v>
       </c>
       <c r="D86" t="n">
-        <v>33.78322516601764</v>
+        <v>40.53987019922116</v>
       </c>
       <c r="E86" t="n">
-        <v>3865.31631873066</v>
+        <v>4638.379582476791</v>
       </c>
       <c r="F86" t="inlineStr"/>
     </row>
@@ -2283,14 +2283,14 @@
         <v>1987</v>
       </c>
       <c r="C87" t="n">
-        <v>563.8970280438901</v>
+        <v>676.6764336526682</v>
       </c>
       <c r="D87" t="n">
-        <v>72.35174638140985</v>
+        <v>86.82209565769185</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>1750.202039942195</v>
+        <v>2100.242447930635</v>
       </c>
     </row>
     <row r="88">
@@ -2303,16 +2303,16 @@
         <v>1988</v>
       </c>
       <c r="C88" t="n">
-        <v>339.0315963613396</v>
+        <v>406.8379156336074</v>
       </c>
       <c r="D88" t="n">
-        <v>5.386361821333769</v>
+        <v>6.463634185600521</v>
       </c>
       <c r="E88" t="n">
-        <v>4495.633270406929</v>
+        <v>5394.759924488313</v>
       </c>
       <c r="F88" t="n">
-        <v>1630.292009142133</v>
+        <v>1956.35041097056</v>
       </c>
     </row>
     <row r="89">
@@ -2325,16 +2325,16 @@
         <v>1989</v>
       </c>
       <c r="C89" t="n">
-        <v>426.0975791298213</v>
+        <v>511.3170949557855</v>
       </c>
       <c r="D89" t="n">
-        <v>10.53272649032989</v>
+        <v>12.63927178839586</v>
       </c>
       <c r="E89" t="n">
-        <v>3522.234196135858</v>
+        <v>4226.681035363031</v>
       </c>
       <c r="F89" t="n">
-        <v>870.7474044887106</v>
+        <v>1044.896885386453</v>
       </c>
     </row>
     <row r="90">
@@ -2347,16 +2347,16 @@
         <v>1990</v>
       </c>
       <c r="C90" t="n">
-        <v>541.6002014412019</v>
+        <v>649.9202417294422</v>
       </c>
       <c r="D90" t="n">
-        <v>14.64782241705421</v>
+        <v>17.57738690046505</v>
       </c>
       <c r="E90" t="n">
-        <v>6845.790629637511</v>
+        <v>8214.948755565014</v>
       </c>
       <c r="F90" t="n">
-        <v>816.4350230676083</v>
+        <v>979.7220276811303</v>
       </c>
     </row>
     <row r="91">
@@ -2369,13 +2369,13 @@
         <v>1991</v>
       </c>
       <c r="C91" t="n">
-        <v>648.9387693665694</v>
+        <v>778.7265232398832</v>
       </c>
       <c r="D91" t="n">
-        <v>8.653368815762475</v>
+        <v>10.38404257891497</v>
       </c>
       <c r="E91" t="n">
-        <v>3826.573811432509</v>
+        <v>4591.88857371901</v>
       </c>
       <c r="F91" t="inlineStr"/>
     </row>
@@ -2389,16 +2389,16 @@
         <v>1992</v>
       </c>
       <c r="C92" t="n">
-        <v>309.0649318203975</v>
+        <v>370.8779181844769</v>
       </c>
       <c r="D92" t="n">
-        <v>5.289589561498899</v>
+        <v>6.347507473798679</v>
       </c>
       <c r="E92" t="n">
-        <v>2077.809166428574</v>
+        <v>2493.370999714289</v>
       </c>
       <c r="F92" t="n">
-        <v>782.2311620668191</v>
+        <v>938.677394480183</v>
       </c>
     </row>
     <row r="93">
@@ -2411,16 +2411,16 @@
         <v>1993</v>
       </c>
       <c r="C93" t="n">
-        <v>394.0646926976543</v>
+        <v>472.877631237185</v>
       </c>
       <c r="D93" t="n">
-        <v>9.658741160238577</v>
+        <v>11.59048939228629</v>
       </c>
       <c r="E93" t="n">
-        <v>3349.603817425647</v>
+        <v>4019.524580910777</v>
       </c>
       <c r="F93" t="n">
-        <v>1139.473644292246</v>
+        <v>1367.368373150696</v>
       </c>
     </row>
     <row r="94">
@@ -2433,16 +2433,16 @@
         <v>1994</v>
       </c>
       <c r="C94" t="n">
-        <v>904.3804227978051</v>
+        <v>1085.256507357366</v>
       </c>
       <c r="D94" t="n">
-        <v>14.95606301422918</v>
+        <v>17.94727561707502</v>
       </c>
       <c r="E94" t="n">
-        <v>2338.593141988471</v>
+        <v>2806.311770386166</v>
       </c>
       <c r="F94" t="n">
-        <v>1690.546202937837</v>
+        <v>2028.655443525404</v>
       </c>
     </row>
     <row r="95">
@@ -2455,16 +2455,16 @@
         <v>1995</v>
       </c>
       <c r="C95" t="n">
-        <v>424.7959703640047</v>
+        <v>509.7551644368058</v>
       </c>
       <c r="D95" t="n">
-        <v>7.980193844527869</v>
+        <v>9.576232613433445</v>
       </c>
       <c r="E95" t="n">
-        <v>2687.544978577406</v>
+        <v>3225.053974292888</v>
       </c>
       <c r="F95" t="n">
-        <v>1026.701703299279</v>
+        <v>1232.042043959136</v>
       </c>
     </row>
     <row r="96">
@@ -2477,16 +2477,16 @@
         <v>1996</v>
       </c>
       <c r="C96" t="n">
-        <v>416.1330797102987</v>
+        <v>499.3596956523585</v>
       </c>
       <c r="D96" t="n">
-        <v>5.830070125185403</v>
+        <v>6.996084150222485</v>
       </c>
       <c r="E96" t="n">
-        <v>1917.358823858252</v>
+        <v>2300.830588629901</v>
       </c>
       <c r="F96" t="n">
-        <v>679.5771462426197</v>
+        <v>815.4925754911436</v>
       </c>
     </row>
     <row r="97">
@@ -2499,16 +2499,16 @@
         <v>1997</v>
       </c>
       <c r="C97" t="n">
-        <v>599.8942257478554</v>
+        <v>719.8730708974265</v>
       </c>
       <c r="D97" t="n">
-        <v>10.77716241750968</v>
+        <v>12.93259490101161</v>
       </c>
       <c r="E97" t="n">
-        <v>3500.279859886025</v>
+        <v>4200.335831863231</v>
       </c>
       <c r="F97" t="n">
-        <v>852.0365592095708</v>
+        <v>1022.443871051485</v>
       </c>
     </row>
     <row r="98">
@@ -2521,16 +2521,16 @@
         <v>1998</v>
       </c>
       <c r="C98" t="n">
-        <v>532.2285694314418</v>
+        <v>638.6742833177299</v>
       </c>
       <c r="D98" t="n">
-        <v>14.82866276135766</v>
+        <v>17.79439531362919</v>
       </c>
       <c r="E98" t="n">
-        <v>4048.211810206681</v>
+        <v>4857.854172248018</v>
       </c>
       <c r="F98" t="n">
-        <v>1100.252283111433</v>
+        <v>1320.302739733719</v>
       </c>
     </row>
     <row r="99">
@@ -2543,16 +2543,16 @@
         <v>1999</v>
       </c>
       <c r="C99" t="n">
-        <v>519.2964044596686</v>
+        <v>623.1556853516021</v>
       </c>
       <c r="D99" t="n">
-        <v>14.08972873674516</v>
+        <v>16.90767448409418</v>
       </c>
       <c r="E99" t="n">
-        <v>5899.771955106919</v>
+        <v>7079.726346128299</v>
       </c>
       <c r="F99" t="n">
-        <v>1773.153639953628</v>
+        <v>2127.784367944353</v>
       </c>
     </row>
     <row r="100">
@@ -2565,16 +2565,16 @@
         <v>2000</v>
       </c>
       <c r="C100" t="n">
-        <v>683.9029780109624</v>
+        <v>820.6835736131554</v>
       </c>
       <c r="D100" t="n">
-        <v>31.02789760020594</v>
+        <v>37.23347712024713</v>
       </c>
       <c r="E100" t="n">
-        <v>10552.4912941688</v>
+        <v>12662.98955300256</v>
       </c>
       <c r="F100" t="n">
-        <v>2577.86217876022</v>
+        <v>3093.434614512265</v>
       </c>
     </row>
     <row r="101">
@@ -2587,16 +2587,16 @@
         <v>2001</v>
       </c>
       <c r="C101" t="n">
-        <v>553.8803714997437</v>
+        <v>664.6564457996925</v>
       </c>
       <c r="D101" t="n">
-        <v>21.28140709500083</v>
+        <v>25.53768851400098</v>
       </c>
       <c r="E101" t="n">
-        <v>4232.592612825022</v>
+        <v>5079.111135390028</v>
       </c>
       <c r="F101" t="n">
-        <v>1477.498966917441</v>
+        <v>1772.998760300929</v>
       </c>
     </row>
     <row r="102">
@@ -2609,16 +2609,16 @@
         <v>2002</v>
       </c>
       <c r="C102" t="n">
-        <v>714.7686737995298</v>
+        <v>857.7224085594355</v>
       </c>
       <c r="D102" t="n">
-        <v>8.61870250809555</v>
+        <v>10.34244300971466</v>
       </c>
       <c r="E102" t="n">
-        <v>2193.886788120488</v>
+        <v>2632.664145744585</v>
       </c>
       <c r="F102" t="n">
-        <v>1257.888931541018</v>
+        <v>1509.466717849222</v>
       </c>
     </row>
     <row r="103">
@@ -2631,16 +2631,16 @@
         <v>2003</v>
       </c>
       <c r="C103" t="n">
-        <v>609.6024253004979</v>
+        <v>731.5229103605973</v>
       </c>
       <c r="D103" t="n">
-        <v>4.378660750720065</v>
+        <v>5.254392900864078</v>
       </c>
       <c r="E103" t="n">
-        <v>1614.894792833506</v>
+        <v>1937.873751400207</v>
       </c>
       <c r="F103" t="n">
-        <v>909.1871985017123</v>
+        <v>1091.024638202054</v>
       </c>
     </row>
     <row r="104">
@@ -2653,16 +2653,16 @@
         <v>2004</v>
       </c>
       <c r="C104" t="n">
-        <v>402.3758715733695</v>
+        <v>482.8510458880432</v>
       </c>
       <c r="D104" t="n">
-        <v>7.903264168385567</v>
+        <v>9.483917002062677</v>
       </c>
       <c r="E104" t="n">
-        <v>1278.224729610259</v>
+        <v>1533.86967553231</v>
       </c>
       <c r="F104" t="n">
-        <v>1106.173876658406</v>
+        <v>1327.408651990087</v>
       </c>
     </row>
     <row r="105">
@@ -2675,16 +2675,16 @@
         <v>2005</v>
       </c>
       <c r="C105" t="n">
-        <v>276.2557678084816</v>
+        <v>331.5069213701777</v>
       </c>
       <c r="D105" t="n">
-        <v>5.16941249090159</v>
+        <v>6.203294989081905</v>
       </c>
       <c r="E105" t="n">
-        <v>999.8011856516082</v>
+        <v>1199.76142278193</v>
       </c>
       <c r="F105" t="n">
-        <v>882.4642945912068</v>
+        <v>1058.957153509448</v>
       </c>
     </row>
     <row r="106">
@@ -2697,16 +2697,16 @@
         <v>2006</v>
       </c>
       <c r="C106" t="n">
-        <v>383.4789652561967</v>
+        <v>460.1747583074363</v>
       </c>
       <c r="D106" t="n">
-        <v>9.701619469353291</v>
+        <v>11.64194336322395</v>
       </c>
       <c r="E106" t="n">
-        <v>2379.684409484527</v>
+        <v>2855.621291381434</v>
       </c>
       <c r="F106" t="n">
-        <v>1533.75219058068</v>
+        <v>1840.502628696817</v>
       </c>
     </row>
     <row r="107">
@@ -2719,16 +2719,16 @@
         <v>2008</v>
       </c>
       <c r="C107" t="n">
-        <v>407.264051760721</v>
+        <v>488.7168621128653</v>
       </c>
       <c r="D107" t="n">
-        <v>13.27872332957156</v>
+        <v>15.93446799548587</v>
       </c>
       <c r="E107" t="n">
-        <v>3042.996397054112</v>
+        <v>3651.595676464933</v>
       </c>
       <c r="F107" t="n">
-        <v>1626.643946712841</v>
+        <v>1951.972736055409</v>
       </c>
     </row>
     <row r="108">
@@ -2741,13 +2741,13 @@
         <v>2010</v>
       </c>
       <c r="C108" t="n">
-        <v>215.3845212393887</v>
+        <v>258.4614254872664</v>
       </c>
       <c r="D108" t="n">
-        <v>6.33999231091919</v>
+        <v>7.607990773103028</v>
       </c>
       <c r="E108" t="n">
-        <v>840.8905494972206</v>
+        <v>1009.068659396665</v>
       </c>
       <c r="F108" t="inlineStr"/>
     </row>
@@ -2761,16 +2761,16 @@
         <v>2011</v>
       </c>
       <c r="C109" t="n">
-        <v>302.0895297420655</v>
+        <v>362.5074356904787</v>
       </c>
       <c r="D109" t="n">
-        <v>9.51308219919377</v>
+        <v>11.41569863903253</v>
       </c>
       <c r="E109" t="n">
-        <v>1649.45706677408</v>
+        <v>1979.348480128897</v>
       </c>
       <c r="F109" t="n">
-        <v>1609.9651963633</v>
+        <v>1931.958235635961</v>
       </c>
     </row>
     <row r="110">
@@ -2783,16 +2783,16 @@
         <v>2012</v>
       </c>
       <c r="C110" t="n">
-        <v>399.0934625316593</v>
+        <v>478.9121550379911</v>
       </c>
       <c r="D110" t="n">
-        <v>10.93957613984765</v>
+        <v>13.12749136781718</v>
       </c>
       <c r="E110" t="n">
-        <v>2924.810095213497</v>
+        <v>3509.772114256197</v>
       </c>
       <c r="F110" t="n">
-        <v>1516.322721238507</v>
+        <v>1819.587265486208</v>
       </c>
     </row>
     <row r="111">
@@ -2805,13 +2805,13 @@
         <v>2013</v>
       </c>
       <c r="C111" t="n">
-        <v>315.2900332862291</v>
+        <v>378.3480399434748</v>
       </c>
       <c r="D111" t="n">
-        <v>8.433474913603842</v>
+        <v>10.12016989632461</v>
       </c>
       <c r="E111" t="n">
-        <v>1696.594734093885</v>
+        <v>2035.913680912662</v>
       </c>
       <c r="F111" t="inlineStr"/>
     </row>
@@ -2825,16 +2825,16 @@
         <v>2015</v>
       </c>
       <c r="C112" t="n">
-        <v>414.8027490826906</v>
+        <v>497.7632988992286</v>
       </c>
       <c r="D112" t="n">
-        <v>6.488915900016568</v>
+        <v>7.786699080019884</v>
       </c>
       <c r="E112" t="n">
-        <v>1052.083489501587</v>
+        <v>1262.500187401904</v>
       </c>
       <c r="F112" t="n">
-        <v>1864.454927503133</v>
+        <v>2237.34591300376</v>
       </c>
     </row>
     <row r="113">
@@ -2847,13 +2847,13 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>342.5104404276134</v>
+        <v>411.0125285131361</v>
       </c>
       <c r="D113" t="n">
-        <v>5.666675734133555</v>
+        <v>6.800010880960264</v>
       </c>
       <c r="E113" t="n">
-        <v>1142.11440885197</v>
+        <v>1370.537290622364</v>
       </c>
       <c r="F113" t="inlineStr"/>
     </row>
@@ -2867,13 +2867,13 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>444.804048428068</v>
+        <v>533.7648581136816</v>
       </c>
       <c r="D114" t="n">
-        <v>7.384500545469453</v>
+        <v>8.861400654563345</v>
       </c>
       <c r="E114" t="n">
-        <v>1767.481021713245</v>
+        <v>2120.977226055894</v>
       </c>
       <c r="F114" t="inlineStr"/>
     </row>
@@ -2887,16 +2887,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>598.9107400224237</v>
+        <v>718.6928880269085</v>
       </c>
       <c r="D115" t="n">
-        <v>12.14031645516297</v>
+        <v>14.56837974619557</v>
       </c>
       <c r="E115" t="n">
-        <v>3253.491083065487</v>
+        <v>3904.189299678584</v>
       </c>
       <c r="F115" t="n">
-        <v>2236.673425274994</v>
+        <v>2684.008110329993</v>
       </c>
     </row>
     <row r="116">
@@ -2909,16 +2909,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>672.2688623660512</v>
+        <v>806.7226348392613</v>
       </c>
       <c r="D116" t="n">
-        <v>28.66818766244727</v>
+        <v>34.40182519493672</v>
       </c>
       <c r="E116" t="n">
-        <v>8603.17426005517</v>
+        <v>10323.8091120662</v>
       </c>
       <c r="F116" t="n">
-        <v>3304.955000562558</v>
+        <v>3965.94600067507</v>
       </c>
     </row>
     <row r="117">
@@ -2931,16 +2931,16 @@
         <v>1998</v>
       </c>
       <c r="C117" t="n">
-        <v>21.82798978607953</v>
+        <v>26.19358774329543</v>
       </c>
       <c r="D117" t="n">
-        <v>0.7906583740643977</v>
+        <v>0.9487900488772769</v>
       </c>
       <c r="E117" t="n">
-        <v>335.5517123045429</v>
+        <v>402.6620547654516</v>
       </c>
       <c r="F117" t="n">
-        <v>40.80857189738048</v>
+        <v>48.97028627685659</v>
       </c>
     </row>
     <row r="118">
@@ -2953,13 +2953,13 @@
         <v>1999</v>
       </c>
       <c r="C118" t="n">
-        <v>19.41522655057976</v>
+        <v>23.29827186069571</v>
       </c>
       <c r="D118" t="n">
-        <v>1.078604430536729</v>
+        <v>1.294325316644074</v>
       </c>
       <c r="E118" t="n">
-        <v>1121.13885951517</v>
+        <v>1345.366631418203</v>
       </c>
       <c r="F118" t="inlineStr"/>
     </row>
@@ -2973,7 +2973,7 @@
         <v>2000</v>
       </c>
       <c r="C119" t="n">
-        <v>21.49917286416997</v>
+        <v>25.79900743700395</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         <v>2001</v>
       </c>
       <c r="C120" t="n">
-        <v>12.61658650731898</v>
+        <v>15.13990380878278</v>
       </c>
       <c r="D120" t="n">
-        <v>0.8141957330746339</v>
+        <v>0.9770348796895605</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
@@ -3007,13 +3007,13 @@
         <v>2002</v>
       </c>
       <c r="C121" t="n">
-        <v>7.570815091659961</v>
+        <v>9.084978109991951</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4754329251994698</v>
+        <v>0.5705195102393636</v>
       </c>
       <c r="E121" t="n">
-        <v>269.3085758452165</v>
+        <v>323.1702910142598</v>
       </c>
       <c r="F121" t="inlineStr"/>
     </row>
@@ -3027,13 +3027,13 @@
         <v>2003</v>
       </c>
       <c r="C122" t="n">
-        <v>14.55529541874719</v>
+        <v>17.46635450249664</v>
       </c>
       <c r="D122" t="n">
-        <v>0.5577961002386697</v>
+        <v>0.6693553202864039</v>
       </c>
       <c r="E122" t="n">
-        <v>321.9783785540299</v>
+        <v>386.374054264836</v>
       </c>
       <c r="F122" t="inlineStr"/>
     </row>
@@ -3047,11 +3047,11 @@
         <v>2004</v>
       </c>
       <c r="C123" t="n">
-        <v>17.54647820999864</v>
+        <v>21.05577385199837</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>300.6225891685597</v>
+        <v>360.7471070022716</v>
       </c>
       <c r="F123" t="inlineStr"/>
     </row>
@@ -3065,13 +3065,13 @@
         <v>2005</v>
       </c>
       <c r="C124" t="n">
-        <v>9.286259981507547</v>
+        <v>11.14351197780905</v>
       </c>
       <c r="D124" t="n">
-        <v>0.5524238187435162</v>
+        <v>0.6629085824922188</v>
       </c>
       <c r="E124" t="n">
-        <v>331.3035819661915</v>
+        <v>397.5642983594295</v>
       </c>
       <c r="F124" t="inlineStr"/>
     </row>
@@ -3085,13 +3085,13 @@
         <v>2006</v>
       </c>
       <c r="C125" t="n">
-        <v>22.89720856445912</v>
+        <v>27.47665027735095</v>
       </c>
       <c r="D125" t="n">
-        <v>1.267521800983396</v>
+        <v>1.521026161180075</v>
       </c>
       <c r="E125" t="n">
-        <v>1031.152707628628</v>
+        <v>1237.383249154354</v>
       </c>
       <c r="F125" t="inlineStr"/>
     </row>
@@ -3105,16 +3105,16 @@
         <v>2011</v>
       </c>
       <c r="C126" t="n">
-        <v>14.77923881261369</v>
+        <v>17.73508657513642</v>
       </c>
       <c r="D126" t="n">
-        <v>1.680478852455246</v>
+        <v>2.016574622946294</v>
       </c>
       <c r="E126" t="n">
-        <v>528.8377829631823</v>
+        <v>634.6053395558189</v>
       </c>
       <c r="F126" t="n">
-        <v>51.23300545699406</v>
+        <v>61.47960654839287</v>
       </c>
     </row>
     <row r="127">
@@ -3127,16 +3127,16 @@
         <v>2012</v>
       </c>
       <c r="C127" t="n">
-        <v>15.96029042303256</v>
+        <v>19.15234850763907</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4282373880286872</v>
+        <v>0.5138848656344245</v>
       </c>
       <c r="E127" t="n">
-        <v>193.8772028633419</v>
+        <v>232.6526434360104</v>
       </c>
       <c r="F127" t="n">
-        <v>55.34818106173935</v>
+        <v>66.41781727408723</v>
       </c>
     </row>
     <row r="128">
@@ -3149,16 +3149,16 @@
         <v>2013</v>
       </c>
       <c r="C128" t="n">
-        <v>10.4719797860435</v>
+        <v>12.5663757432522</v>
       </c>
       <c r="D128" t="n">
-        <v>1.253225645828915</v>
+        <v>1.503870774994698</v>
       </c>
       <c r="E128" t="n">
-        <v>966.9861441338189</v>
+        <v>1160.383372960583</v>
       </c>
       <c r="F128" t="n">
-        <v>65.00929877296122</v>
+        <v>78.01115852755343</v>
       </c>
     </row>
     <row r="129">
@@ -3171,16 +3171,16 @@
         <v>2014</v>
       </c>
       <c r="C129" t="n">
-        <v>15.66342971472917</v>
+        <v>18.796115657675</v>
       </c>
       <c r="D129" t="n">
-        <v>0.9791915177608516</v>
+        <v>1.175029821313021</v>
       </c>
       <c r="E129" t="n">
-        <v>699.1844647077061</v>
+        <v>839.0213576492474</v>
       </c>
       <c r="F129" t="n">
-        <v>100.1414218444871</v>
+        <v>120.1697062133845</v>
       </c>
     </row>
     <row r="130">
@@ -3193,16 +3193,16 @@
         <v>2015</v>
       </c>
       <c r="C130" t="n">
-        <v>14.59327701163174</v>
+        <v>17.5119324139581</v>
       </c>
       <c r="D130" t="n">
-        <v>0.6775456860608734</v>
+        <v>0.8130548232730483</v>
       </c>
       <c r="E130" t="n">
-        <v>419.1733788617973</v>
+        <v>503.0080546341568</v>
       </c>
       <c r="F130" t="n">
-        <v>80.60445597392822</v>
+        <v>96.72534716871388</v>
       </c>
     </row>
     <row r="131">
@@ -3215,16 +3215,16 @@
         <v>2016</v>
       </c>
       <c r="C131" t="n">
-        <v>9.756235006538578</v>
+        <v>11.70748200784629</v>
       </c>
       <c r="D131" t="n">
-        <v>1.21195358981344</v>
+        <v>1.454344307776128</v>
       </c>
       <c r="E131" t="n">
-        <v>250.5892148403428</v>
+        <v>300.7070578084114</v>
       </c>
       <c r="F131" t="n">
-        <v>63.37160775859282</v>
+        <v>76.04592931031137</v>
       </c>
     </row>
     <row r="132">
@@ -3237,16 +3237,16 @@
         <v>2018</v>
       </c>
       <c r="C132" t="n">
-        <v>15.93901009835165</v>
+        <v>19.12681211802197</v>
       </c>
       <c r="D132" t="n">
-        <v>0.4457764240631753</v>
+        <v>0.5349317088758103</v>
       </c>
       <c r="E132" t="n">
-        <v>269.2312658257636</v>
+        <v>323.0775189909162</v>
       </c>
       <c r="F132" t="n">
-        <v>60.91200159074388</v>
+        <v>73.09440190889266</v>
       </c>
     </row>
     <row r="133">
@@ -3259,16 +3259,16 @@
         <v>2019</v>
       </c>
       <c r="C133" t="n">
-        <v>28.93660473343259</v>
+        <v>34.72392568011911</v>
       </c>
       <c r="D133" t="n">
-        <v>1.43739550275823</v>
+        <v>1.724874603309876</v>
       </c>
       <c r="E133" t="n">
-        <v>776.0854103613681</v>
+        <v>931.3024924336419</v>
       </c>
       <c r="F133" t="n">
-        <v>84.3493768756538</v>
+        <v>101.2192522507846</v>
       </c>
     </row>
     <row r="134">
@@ -3281,16 +3281,16 @@
         <v>2020</v>
       </c>
       <c r="C134" t="n">
-        <v>22.76835184088262</v>
+        <v>27.32202220905914</v>
       </c>
       <c r="D134" t="n">
-        <v>0.805469630699035</v>
+        <v>0.9665635568388418</v>
       </c>
       <c r="E134" t="n">
-        <v>315.5125163713641</v>
+        <v>378.6150196456369</v>
       </c>
       <c r="F134" t="n">
-        <v>98.35708933618547</v>
+        <v>118.0285072034226</v>
       </c>
     </row>
     <row r="135">
@@ -3303,16 +3303,16 @@
         <v>1995</v>
       </c>
       <c r="C135" t="n">
-        <v>43.20137400451075</v>
+        <v>51.84164880541291</v>
       </c>
       <c r="D135" t="n">
-        <v>1.261319622470048</v>
+        <v>1.513583546964058</v>
       </c>
       <c r="E135" t="n">
-        <v>430.5322911701562</v>
+        <v>516.6387494041873</v>
       </c>
       <c r="F135" t="n">
-        <v>176.8852387337406</v>
+        <v>212.2622864804887</v>
       </c>
     </row>
     <row r="136">
@@ -3325,16 +3325,16 @@
         <v>1996</v>
       </c>
       <c r="C136" t="n">
-        <v>42.32975369646419</v>
+        <v>50.79570443575703</v>
       </c>
       <c r="D136" t="n">
-        <v>1.085266248247397</v>
+        <v>1.302319497896878</v>
       </c>
       <c r="E136" t="n">
-        <v>384.7915608514137</v>
+        <v>461.7498730216965</v>
       </c>
       <c r="F136" t="n">
-        <v>143.6288757627007</v>
+        <v>172.3546509152409</v>
       </c>
     </row>
     <row r="137">
@@ -3347,16 +3347,16 @@
         <v>1997</v>
       </c>
       <c r="C137" t="n">
-        <v>30.7886815030627</v>
+        <v>36.94641780367524</v>
       </c>
       <c r="D137" t="n">
-        <v>1.162051872151194</v>
+        <v>1.394462246581433</v>
       </c>
       <c r="E137" t="n">
-        <v>428.4688124828462</v>
+        <v>514.1625749794155</v>
       </c>
       <c r="F137" t="n">
-        <v>128.6679451635399</v>
+        <v>154.4015341962478</v>
       </c>
     </row>
     <row r="138">
@@ -3369,16 +3369,16 @@
         <v>1998</v>
       </c>
       <c r="C138" t="n">
-        <v>36.94448436197132</v>
+        <v>44.33338123436558</v>
       </c>
       <c r="D138" t="n">
-        <v>1.682400057017694</v>
+        <v>2.018880068421233</v>
       </c>
       <c r="E138" t="n">
-        <v>637.1842858735313</v>
+        <v>764.6211430482372</v>
       </c>
       <c r="F138" t="n">
-        <v>175.9291755540946</v>
+        <v>211.1150106649136</v>
       </c>
     </row>
     <row r="139">
@@ -3391,16 +3391,16 @@
         <v>1999</v>
       </c>
       <c r="C139" t="n">
-        <v>60.88915283023869</v>
+        <v>73.0669833962864</v>
       </c>
       <c r="D139" t="n">
-        <v>3.273467950963915</v>
+        <v>3.928161541156698</v>
       </c>
       <c r="E139" t="n">
-        <v>1481.66301410922</v>
+        <v>1777.995616931064</v>
       </c>
       <c r="F139" t="n">
-        <v>332.185908457374</v>
+        <v>398.6230901488487</v>
       </c>
     </row>
     <row r="140">
@@ -3413,16 +3413,16 @@
         <v>2000</v>
       </c>
       <c r="C140" t="n">
-        <v>63.48058038141561</v>
+        <v>76.17669645769872</v>
       </c>
       <c r="D140" t="n">
-        <v>3.812702042892715</v>
+        <v>4.575242451471255</v>
       </c>
       <c r="E140" t="n">
-        <v>1151.415594585329</v>
+        <v>1381.698713502394</v>
       </c>
       <c r="F140" t="n">
-        <v>428.7557406319572</v>
+        <v>514.5068887583486</v>
       </c>
     </row>
     <row r="141">
@@ -3435,16 +3435,16 @@
         <v>2001</v>
       </c>
       <c r="C141" t="n">
-        <v>43.83372228170499</v>
+        <v>52.60046673804597</v>
       </c>
       <c r="D141" t="n">
-        <v>1.566493047153545</v>
+        <v>1.879791656584253</v>
       </c>
       <c r="E141" t="n">
-        <v>344.6645518909453</v>
+        <v>413.5974622691346</v>
       </c>
       <c r="F141" t="n">
-        <v>224.7171589006246</v>
+        <v>269.6605906807495</v>
       </c>
     </row>
     <row r="142">
@@ -3457,16 +3457,16 @@
         <v>2002</v>
       </c>
       <c r="C142" t="n">
-        <v>39.15298310684493</v>
+        <v>46.98357972821391</v>
       </c>
       <c r="D142" t="n">
-        <v>1.296743224244016</v>
+        <v>1.55609186909282</v>
       </c>
       <c r="E142" t="n">
-        <v>289.0914156518298</v>
+        <v>346.9096987821957</v>
       </c>
       <c r="F142" t="n">
-        <v>195.8159412158462</v>
+        <v>234.9791294590155</v>
       </c>
     </row>
     <row r="143">
@@ -3479,16 +3479,16 @@
         <v>2003</v>
       </c>
       <c r="C143" t="n">
-        <v>59.26498380326215</v>
+        <v>71.11798056391461</v>
       </c>
       <c r="D143" t="n">
-        <v>1.496223700735488</v>
+        <v>1.795468440882586</v>
       </c>
       <c r="E143" t="n">
-        <v>236.623580022185</v>
+        <v>283.9482960266221</v>
       </c>
       <c r="F143" t="n">
-        <v>187.050520337289</v>
+        <v>224.4606244047468</v>
       </c>
     </row>
     <row r="144">
@@ -3501,16 +3501,16 @@
         <v>2004</v>
       </c>
       <c r="C144" t="n">
-        <v>40.28778276183817</v>
+        <v>48.3453393142058</v>
       </c>
       <c r="D144" t="n">
-        <v>1.173397412360143</v>
+        <v>1.408076894832172</v>
       </c>
       <c r="E144" t="n">
-        <v>175.0898537937713</v>
+        <v>210.1078245525255</v>
       </c>
       <c r="F144" t="n">
-        <v>178.6440552342183</v>
+        <v>214.3728662810618</v>
       </c>
     </row>
     <row r="145">
@@ -3523,16 +3523,16 @@
         <v>2005</v>
       </c>
       <c r="C145" t="n">
-        <v>35.42931818168498</v>
+        <v>42.51518181802197</v>
       </c>
       <c r="D145" t="n">
-        <v>0.8923468529323221</v>
+        <v>1.070816223518787</v>
       </c>
       <c r="E145" t="n">
-        <v>190.6210161803414</v>
+        <v>228.7452194164096</v>
       </c>
       <c r="F145" t="n">
-        <v>168.09112907935</v>
+        <v>201.7093548952199</v>
       </c>
     </row>
     <row r="146">
@@ -3545,16 +3545,16 @@
         <v>2006</v>
       </c>
       <c r="C146" t="n">
-        <v>72.15775280648346</v>
+        <v>86.58930336778015</v>
       </c>
       <c r="D146" t="n">
-        <v>2.312592906230066</v>
+        <v>2.775111487476079</v>
       </c>
       <c r="E146" t="n">
-        <v>517.3090331643402</v>
+        <v>620.7708397972081</v>
       </c>
       <c r="F146" t="n">
-        <v>315.0965301846499</v>
+        <v>378.1158362215797</v>
       </c>
     </row>
     <row r="147">
@@ -3567,16 +3567,16 @@
         <v>2007</v>
       </c>
       <c r="C147" t="n">
-        <v>42.525725321428</v>
+        <v>51.03087038571355</v>
       </c>
       <c r="D147" t="n">
-        <v>1.925476594795005</v>
+        <v>2.310571913754004</v>
       </c>
       <c r="E147" t="n">
-        <v>529.4723937237975</v>
+        <v>635.3668724685566</v>
       </c>
       <c r="F147" t="n">
-        <v>192.6121906718114</v>
+        <v>231.1346288061736</v>
       </c>
     </row>
     <row r="148">
@@ -3589,16 +3589,16 @@
         <v>2008</v>
       </c>
       <c r="C148" t="n">
-        <v>54.50924165808345</v>
+        <v>65.41108998970012</v>
       </c>
       <c r="D148" t="n">
-        <v>2.718853676573134</v>
+        <v>3.262624411887761</v>
       </c>
       <c r="E148" t="n">
-        <v>726.9747307022848</v>
+        <v>872.3696768427416</v>
       </c>
       <c r="F148" t="n">
-        <v>321.9162259926705</v>
+        <v>386.2994711912046</v>
       </c>
     </row>
     <row r="149">
@@ -3611,16 +3611,16 @@
         <v>2010</v>
       </c>
       <c r="C149" t="n">
-        <v>40.71766627027407</v>
+        <v>48.86119952432888</v>
       </c>
       <c r="D149" t="n">
-        <v>1.599326527037739</v>
+        <v>1.919191832445285</v>
       </c>
       <c r="E149" t="n">
-        <v>500.6418738911458</v>
+        <v>600.7702486693747</v>
       </c>
       <c r="F149" t="n">
-        <v>168.6949906927315</v>
+        <v>202.4339888312778</v>
       </c>
     </row>
     <row r="150">
@@ -3633,16 +3633,16 @@
         <v>2011</v>
       </c>
       <c r="C150" t="n">
-        <v>54.97092429763331</v>
+        <v>65.96510915715997</v>
       </c>
       <c r="D150" t="n">
-        <v>2.820577901046711</v>
+        <v>3.384693481256054</v>
       </c>
       <c r="E150" t="n">
-        <v>1022.831967307919</v>
+        <v>1227.398360769503</v>
       </c>
       <c r="F150" t="n">
-        <v>308.1332520069056</v>
+        <v>369.7599024082867</v>
       </c>
     </row>
     <row r="151">
@@ -3655,16 +3655,16 @@
         <v>2012</v>
       </c>
       <c r="C151" t="n">
-        <v>47.1433740748163</v>
+        <v>56.57204888977957</v>
       </c>
       <c r="D151" t="n">
-        <v>2.360650338445773</v>
+        <v>2.832780406134927</v>
       </c>
       <c r="E151" t="n">
-        <v>810.1604837704916</v>
+        <v>972.1925805245899</v>
       </c>
       <c r="F151" t="n">
-        <v>284.2200128459098</v>
+        <v>341.0640154150917</v>
       </c>
     </row>
     <row r="152">
@@ -3677,16 +3677,16 @@
         <v>2013</v>
       </c>
       <c r="C152" t="n">
-        <v>52.90748911779683</v>
+        <v>63.48898694135619</v>
       </c>
       <c r="D152" t="n">
-        <v>3.212582659749853</v>
+        <v>3.855099191699822</v>
       </c>
       <c r="E152" t="n">
-        <v>973.3917427392341</v>
+        <v>1168.07009128708</v>
       </c>
       <c r="F152" t="n">
-        <v>292.9160040032267</v>
+        <v>351.499204803872</v>
       </c>
     </row>
     <row r="153">
@@ -3699,16 +3699,16 @@
         <v>2015</v>
       </c>
       <c r="C153" t="n">
-        <v>47.51180336485282</v>
+        <v>57.01416403782338</v>
       </c>
       <c r="D153" t="n">
-        <v>1.992790082049349</v>
+        <v>2.391348098459219</v>
       </c>
       <c r="E153" t="n">
-        <v>628.3742502767315</v>
+        <v>754.0491003320777</v>
       </c>
       <c r="F153" t="n">
-        <v>341.5325004581801</v>
+        <v>409.839000549816</v>
       </c>
     </row>
     <row r="154">
@@ -3721,16 +3721,16 @@
         <v>2016</v>
       </c>
       <c r="C154" t="n">
-        <v>36.59422765172685</v>
+        <v>43.9130731820722</v>
       </c>
       <c r="D154" t="n">
-        <v>1.906034377444126</v>
+        <v>2.287241252932952</v>
       </c>
       <c r="E154" t="n">
-        <v>937.6644980888514</v>
+        <v>1125.197397706622</v>
       </c>
       <c r="F154" t="n">
-        <v>264.2084464709084</v>
+        <v>317.05013576509</v>
       </c>
     </row>
     <row r="155">
@@ -3743,13 +3743,13 @@
         <v>2017</v>
       </c>
       <c r="C155" t="n">
-        <v>37.46366350848653</v>
+        <v>44.95639621018385</v>
       </c>
       <c r="D155" t="n">
-        <v>1.502518695519668</v>
+        <v>1.803022434623602</v>
       </c>
       <c r="E155" t="n">
-        <v>429.3418128560156</v>
+        <v>515.2101754272189</v>
       </c>
       <c r="F155" t="inlineStr"/>
     </row>
@@ -3763,13 +3763,13 @@
         <v>2018</v>
       </c>
       <c r="C156" t="n">
-        <v>54.10353225591221</v>
+        <v>64.92423870709464</v>
       </c>
       <c r="D156" t="n">
-        <v>1.564985060010706</v>
+        <v>1.877982072012848</v>
       </c>
       <c r="E156" t="n">
-        <v>461.9444449155314</v>
+        <v>554.3333338986376</v>
       </c>
       <c r="F156" t="inlineStr"/>
     </row>
@@ -3783,16 +3783,16 @@
         <v>2019</v>
       </c>
       <c r="C157" t="n">
-        <v>67.09114730954367</v>
+        <v>80.50937677145238</v>
       </c>
       <c r="D157" t="n">
-        <v>2.474020170202845</v>
+        <v>2.968824204243413</v>
       </c>
       <c r="E157" t="n">
-        <v>795.471797955112</v>
+        <v>954.5661575461341</v>
       </c>
       <c r="F157" t="n">
-        <v>437.0628405198718</v>
+        <v>524.4754086238461</v>
       </c>
     </row>
     <row r="158">
@@ -3805,16 +3805,16 @@
         <v>2020</v>
       </c>
       <c r="C158" t="n">
-        <v>59.8643647414557</v>
+        <v>71.8372376897468</v>
       </c>
       <c r="D158" t="n">
-        <v>3.172601770982808</v>
+        <v>3.80712212517937</v>
       </c>
       <c r="E158" t="n">
-        <v>1120.665798887265</v>
+        <v>1344.798958664718</v>
       </c>
       <c r="F158" t="n">
-        <v>486.5067623954724</v>
+        <v>583.808114874567</v>
       </c>
     </row>
     <row r="159">
@@ -3827,16 +3827,16 @@
         <v>2022</v>
       </c>
       <c r="C159" t="n">
-        <v>32.05956081351491</v>
+        <v>38.47147297621791</v>
       </c>
       <c r="D159" t="n">
-        <v>1.310037754387346</v>
+        <v>1.572045305264815</v>
       </c>
       <c r="E159" t="n">
-        <v>285.310880899187</v>
+        <v>342.3730570790243</v>
       </c>
       <c r="F159" t="n">
-        <v>213.9680118729835</v>
+        <v>256.7616142475802</v>
       </c>
     </row>
     <row r="160">
@@ -3849,16 +3849,16 @@
         <v>2023</v>
       </c>
       <c r="C160" t="n">
-        <v>58.005743272392</v>
+        <v>69.60689192687042</v>
       </c>
       <c r="D160" t="n">
-        <v>3.982955779020421</v>
+        <v>4.779546934824506</v>
       </c>
       <c r="E160" t="n">
-        <v>1035.530837661209</v>
+        <v>1242.637005193451</v>
       </c>
       <c r="F160" t="n">
-        <v>660.7713120999218</v>
+        <v>792.9255745199064</v>
       </c>
     </row>
     <row r="161">
@@ -3871,16 +3871,16 @@
         <v>2024</v>
       </c>
       <c r="C161" t="n">
-        <v>47.33462348472926</v>
+        <v>56.80154818167514</v>
       </c>
       <c r="D161" t="n">
-        <v>1.964869080369083</v>
+        <v>2.3578428964429</v>
       </c>
       <c r="E161" t="n">
-        <v>531.7472594728408</v>
+        <v>638.0967113674089</v>
       </c>
       <c r="F161" t="n">
-        <v>435.3888207029107</v>
+        <v>522.4665848434929</v>
       </c>
     </row>
     <row r="162">
@@ -3893,16 +3893,16 @@
         <v>2017</v>
       </c>
       <c r="C162" t="n">
-        <v>44.8936129068021</v>
+        <v>53.87233548816253</v>
       </c>
       <c r="D162" t="n">
-        <v>1.954405618927778</v>
+        <v>2.345286742713334</v>
       </c>
       <c r="E162" t="n">
-        <v>777.1116220338538</v>
+        <v>932.5339464406246</v>
       </c>
       <c r="F162" t="n">
-        <v>535.2481834166693</v>
+        <v>642.2978201000033</v>
       </c>
     </row>
     <row r="163">
@@ -3915,16 +3915,16 @@
         <v>2018</v>
       </c>
       <c r="C163" t="n">
-        <v>86.83469252730305</v>
+        <v>104.2016310327637</v>
       </c>
       <c r="D163" t="n">
-        <v>2.262049442825004</v>
+        <v>2.714459331390005</v>
       </c>
       <c r="E163" t="n">
-        <v>1034.116445823784</v>
+        <v>1240.93973498854</v>
       </c>
       <c r="F163" t="n">
-        <v>687.4153924254158</v>
+        <v>824.898470910499</v>
       </c>
     </row>
     <row r="164">
@@ -3937,16 +3937,16 @@
         <v>2019</v>
       </c>
       <c r="C164" t="n">
-        <v>126.011616970958</v>
+        <v>151.2139403651497</v>
       </c>
       <c r="D164" t="n">
-        <v>3.214688287935231</v>
+        <v>3.857625945522277</v>
       </c>
       <c r="E164" t="n">
-        <v>1426.604590032961</v>
+        <v>1711.925508039553</v>
       </c>
       <c r="F164" t="n">
-        <v>895.7901087042121</v>
+        <v>1074.948130445055</v>
       </c>
     </row>
     <row r="165">
@@ -3959,16 +3959,16 @@
         <v>2020</v>
       </c>
       <c r="C165" t="n">
-        <v>112.0509340255936</v>
+        <v>134.4611208307123</v>
       </c>
       <c r="D165" t="n">
-        <v>5.948167481244513</v>
+        <v>7.137800977493417</v>
       </c>
       <c r="E165" t="n">
-        <v>2406.153437801333</v>
+        <v>2887.3841253616</v>
       </c>
       <c r="F165" t="n">
-        <v>1159.623918140276</v>
+        <v>1391.548701768331</v>
       </c>
     </row>
     <row r="166">
@@ -3981,16 +3981,16 @@
         <v>2021</v>
       </c>
       <c r="C166" t="n">
-        <v>70.79610061866926</v>
+        <v>84.95532074240312</v>
       </c>
       <c r="D166" t="n">
-        <v>5.804171207971129</v>
+        <v>6.965005449565357</v>
       </c>
       <c r="E166" t="n">
-        <v>4342.626134634939</v>
+        <v>5211.151361561927</v>
       </c>
       <c r="F166" t="n">
-        <v>618.4678202867691</v>
+        <v>742.161384344123</v>
       </c>
     </row>
     <row r="167">
@@ -4003,16 +4003,16 @@
         <v>2022</v>
       </c>
       <c r="C167" t="n">
-        <v>29.55304332075939</v>
+        <v>35.46365198491126</v>
       </c>
       <c r="D167" t="n">
-        <v>0.9448210542740572</v>
+        <v>1.133785265128868</v>
       </c>
       <c r="E167" t="n">
-        <v>257.7373332608099</v>
+        <v>309.2847999129718</v>
       </c>
       <c r="F167" t="n">
-        <v>316.5694369067731</v>
+        <v>379.8833242881275</v>
       </c>
     </row>
     <row r="168">
@@ -4025,16 +4025,16 @@
         <v>2023</v>
       </c>
       <c r="C168" t="n">
-        <v>79.07649327547209</v>
+        <v>94.8917919305665</v>
       </c>
       <c r="D168" t="n">
-        <v>5.428475939929966</v>
+        <v>6.514171127915957</v>
       </c>
       <c r="E168" t="n">
-        <v>3716.23140989222</v>
+        <v>4459.477691870663</v>
       </c>
       <c r="F168" t="n">
-        <v>996.8818786705847</v>
+        <v>1196.258254404701</v>
       </c>
     </row>
     <row r="169">
@@ -4047,16 +4047,16 @@
         <v>2024</v>
       </c>
       <c r="C169" t="n">
-        <v>66.0944743434578</v>
+        <v>79.31336921214933</v>
       </c>
       <c r="D169" t="n">
-        <v>3.417827418423417</v>
+        <v>4.101392902108101</v>
       </c>
       <c r="E169" t="n">
-        <v>3051.501068608462</v>
+        <v>3661.801282330153</v>
       </c>
       <c r="F169" t="n">
-        <v>537.8286770254263</v>
+        <v>645.3944124305115</v>
       </c>
     </row>
     <row r="170">
@@ -4069,16 +4069,16 @@
         <v>2017</v>
       </c>
       <c r="C170" t="n">
-        <v>7.653335082673016</v>
+        <v>9.184002099207618</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2990016163709289</v>
+        <v>0.3588019396451147</v>
       </c>
       <c r="E170" t="n">
-        <v>85.01488980970291</v>
+        <v>102.0178677716435</v>
       </c>
       <c r="F170" t="n">
-        <v>103.9936630843641</v>
+        <v>124.792395701237</v>
       </c>
     </row>
     <row r="171">
@@ -4091,16 +4091,16 @@
         <v>2018</v>
       </c>
       <c r="C171" t="n">
-        <v>12.03966443157236</v>
+        <v>14.44759731788683</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3228871252526269</v>
+        <v>0.3874645503031524</v>
       </c>
       <c r="E171" t="n">
-        <v>147.4724929738897</v>
+        <v>176.9669915686676</v>
       </c>
       <c r="F171" t="n">
-        <v>132.1199194463231</v>
+        <v>158.5439033355878</v>
       </c>
     </row>
     <row r="172">
@@ -4113,16 +4113,16 @@
         <v>2019</v>
       </c>
       <c r="C172" t="n">
-        <v>15.61902044698713</v>
+        <v>18.74282453638455</v>
       </c>
       <c r="D172" t="n">
-        <v>0.5149084598850812</v>
+        <v>0.6178901518620976</v>
       </c>
       <c r="E172" t="n">
-        <v>220.4319626434661</v>
+        <v>264.5183551721593</v>
       </c>
       <c r="F172" t="n">
-        <v>194.6953311163847</v>
+        <v>233.6343973396616</v>
       </c>
     </row>
     <row r="173">
@@ -4135,16 +4135,16 @@
         <v>2020</v>
       </c>
       <c r="C173" t="n">
-        <v>18.06037046155562</v>
+        <v>21.67244455386674</v>
       </c>
       <c r="D173" t="n">
-        <v>1.091211164162206</v>
+        <v>1.309453396994647</v>
       </c>
       <c r="E173" t="n">
-        <v>441.1929326302305</v>
+        <v>529.4315191562764</v>
       </c>
       <c r="F173" t="n">
-        <v>260.8764771218694</v>
+        <v>313.0517725462432</v>
       </c>
     </row>
     <row r="174">
@@ -4157,16 +4157,16 @@
         <v>2021</v>
       </c>
       <c r="C174" t="n">
-        <v>11.9192719775834</v>
+        <v>14.30312637310008</v>
       </c>
       <c r="D174" t="n">
-        <v>0.4518888122294344</v>
+        <v>0.5422665746753212</v>
       </c>
       <c r="E174" t="n">
-        <v>131.4454693391129</v>
+        <v>157.7345632069356</v>
       </c>
       <c r="F174" t="n">
-        <v>138.0941476993935</v>
+        <v>165.7129772392721</v>
       </c>
     </row>
     <row r="175">
@@ -4179,16 +4179,16 @@
         <v>2022</v>
       </c>
       <c r="C175" t="n">
-        <v>4.786743207130849</v>
+        <v>5.744091848557019</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1543206847131022</v>
+        <v>0.1851848216557226</v>
       </c>
       <c r="E175" t="n">
-        <v>39.90007417307307</v>
+        <v>47.88008900768768</v>
       </c>
       <c r="F175" t="n">
-        <v>67.31792001127344</v>
+        <v>80.78150401352812</v>
       </c>
     </row>
     <row r="176">
@@ -4201,16 +4201,16 @@
         <v>2023</v>
       </c>
       <c r="C176" t="n">
-        <v>12.53987373993574</v>
+        <v>15.04784848792289</v>
       </c>
       <c r="D176" t="n">
-        <v>0.5328793368597894</v>
+        <v>0.6394552042317473</v>
       </c>
       <c r="E176" t="n">
-        <v>425.7667401549494</v>
+        <v>510.9200881859394</v>
       </c>
       <c r="F176" t="n">
-        <v>192.2764433350712</v>
+        <v>230.7317320020855</v>
       </c>
     </row>
     <row r="177">
@@ -4223,16 +4223,16 @@
         <v>2024</v>
       </c>
       <c r="C177" t="n">
-        <v>11.72027945954619</v>
+        <v>14.06433535145543</v>
       </c>
       <c r="D177" t="n">
-        <v>0.4452999970904939</v>
+        <v>0.5343599965085927</v>
       </c>
       <c r="E177" t="n">
-        <v>180.0605327026289</v>
+        <v>216.0726392431546</v>
       </c>
       <c r="F177" t="n">
-        <v>159.4952462388311</v>
+        <v>191.3942954865973</v>
       </c>
     </row>
     <row r="178">
@@ -4245,13 +4245,13 @@
         <v>2005</v>
       </c>
       <c r="C178" t="n">
-        <v>30.08828549252898</v>
+        <v>36.10594259103476</v>
       </c>
       <c r="D178" t="n">
-        <v>1.306904181090203</v>
+        <v>1.568285017308244</v>
       </c>
       <c r="E178" t="n">
-        <v>251.3824280898642</v>
+        <v>301.6589137078369</v>
       </c>
       <c r="F178" t="inlineStr"/>
     </row>
@@ -4265,13 +4265,13 @@
         <v>2006</v>
       </c>
       <c r="C179" t="n">
-        <v>45.80730229851503</v>
+        <v>54.96876275821803</v>
       </c>
       <c r="D179" t="n">
-        <v>1.542782453446114</v>
+        <v>1.851338944135336</v>
       </c>
       <c r="E179" t="n">
-        <v>1092.910624664672</v>
+        <v>1311.492749597605</v>
       </c>
       <c r="F179" t="inlineStr"/>
     </row>
@@ -4285,13 +4285,13 @@
         <v>2008</v>
       </c>
       <c r="C180" t="n">
-        <v>50.82562563783875</v>
+        <v>60.99075076540651</v>
       </c>
       <c r="D180" t="n">
-        <v>1.778162964553974</v>
+        <v>2.133795557464769</v>
       </c>
       <c r="E180" t="n">
-        <v>419.3053838455864</v>
+        <v>503.1664606147037</v>
       </c>
       <c r="F180" t="inlineStr"/>
     </row>
@@ -4305,13 +4305,13 @@
         <v>2009</v>
       </c>
       <c r="C181" t="n">
-        <v>29.99469304554663</v>
+        <v>35.99363165465594</v>
       </c>
       <c r="D181" t="n">
-        <v>0.8307283887440702</v>
+        <v>0.9968740664928842</v>
       </c>
       <c r="E181" t="n">
-        <v>216.1408557133923</v>
+        <v>259.3690268560707</v>
       </c>
       <c r="F181" t="inlineStr"/>
     </row>
@@ -4325,13 +4325,13 @@
         <v>2011</v>
       </c>
       <c r="C182" t="n">
-        <v>32.4677649478005</v>
+        <v>38.9613179373606</v>
       </c>
       <c r="D182" t="n">
-        <v>1.725613511301057</v>
+        <v>2.070736213561269</v>
       </c>
       <c r="E182" t="n">
-        <v>518.6740582729315</v>
+        <v>622.4088699275176</v>
       </c>
       <c r="F182" t="inlineStr"/>
     </row>
@@ -4345,7 +4345,7 @@
         <v>2012</v>
       </c>
       <c r="C183" t="n">
-        <v>51.03955485954243</v>
+        <v>61.24746583145092</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -4361,13 +4361,13 @@
         <v>2013</v>
       </c>
       <c r="C184" t="n">
-        <v>33.98446680437877</v>
+        <v>40.78136016525453</v>
       </c>
       <c r="D184" t="n">
-        <v>2.096585820542499</v>
+        <v>2.515902984650999</v>
       </c>
       <c r="E184" t="n">
-        <v>694.8628432931899</v>
+        <v>833.8354119518281</v>
       </c>
       <c r="F184" t="inlineStr"/>
     </row>
@@ -4381,13 +4381,13 @@
         <v>2014</v>
       </c>
       <c r="C185" t="n">
-        <v>32.54327205447498</v>
+        <v>39.05192646536998</v>
       </c>
       <c r="D185" t="n">
-        <v>1.165580045080622</v>
+        <v>1.398696054096747</v>
       </c>
       <c r="E185" t="n">
-        <v>317.3426354189075</v>
+        <v>380.8111625026891</v>
       </c>
       <c r="F185" t="inlineStr"/>
     </row>
@@ -4401,13 +4401,13 @@
         <v>2015</v>
       </c>
       <c r="C186" t="n">
-        <v>41.84124163234781</v>
+        <v>50.20948995881738</v>
       </c>
       <c r="D186" t="n">
-        <v>1.698535319620307</v>
+        <v>2.038242383544368</v>
       </c>
       <c r="E186" t="n">
-        <v>458.3240889965408</v>
+        <v>549.9889067958491</v>
       </c>
       <c r="F186" t="inlineStr"/>
     </row>
@@ -4421,13 +4421,13 @@
         <v>2016</v>
       </c>
       <c r="C187" t="n">
-        <v>28.91287455419892</v>
+        <v>34.69544946503871</v>
       </c>
       <c r="D187" t="n">
-        <v>1.214253429475996</v>
+        <v>1.457104115371196</v>
       </c>
       <c r="E187" t="n">
-        <v>581.6187184435531</v>
+        <v>697.9424621322642</v>
       </c>
       <c r="F187" t="inlineStr"/>
     </row>
@@ -4441,13 +4441,13 @@
         <v>2017</v>
       </c>
       <c r="C188" t="n">
-        <v>35.67489863703614</v>
+        <v>42.80987836444336</v>
       </c>
       <c r="D188" t="n">
-        <v>1.782106060485519</v>
+        <v>2.138527272582623</v>
       </c>
       <c r="E188" t="n">
-        <v>520.5710014138863</v>
+        <v>624.6852016966637</v>
       </c>
       <c r="F188" t="inlineStr"/>
     </row>
@@ -4461,13 +4461,13 @@
         <v>2018</v>
       </c>
       <c r="C189" t="n">
-        <v>24.52463867835253</v>
+        <v>29.42956641402305</v>
       </c>
       <c r="D189" t="n">
-        <v>0.7004360797368733</v>
+        <v>0.8405232956842483</v>
       </c>
       <c r="E189" t="n">
-        <v>307.6836546989502</v>
+        <v>369.2203856387403</v>
       </c>
       <c r="F189" t="inlineStr"/>
     </row>
@@ -4481,13 +4481,13 @@
         <v>2019</v>
       </c>
       <c r="C190" t="n">
-        <v>72.94668875104215</v>
+        <v>87.5360265012506</v>
       </c>
       <c r="D190" t="n">
-        <v>2.312223164220635</v>
+        <v>2.774667797064762</v>
       </c>
       <c r="E190" t="n">
-        <v>592.64839123581</v>
+        <v>711.1780694829719</v>
       </c>
       <c r="F190" t="inlineStr"/>
     </row>
@@ -4592,13 +4592,13 @@
         <v>0.3975873918299724</v>
       </c>
       <c r="H2" t="n">
-        <v>1.936147326445069</v>
+        <v>2.32337679173408</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2585155248024</v>
+        <v>6.310218629762883</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.574024278567967</v>
+        <v>-1.888829134281557</v>
       </c>
     </row>
     <row r="3">
@@ -4636,13 +4636,13 @@
         <v>0.1585702494967551</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3330584321370474</v>
+        <v>0.3996701185644567</v>
       </c>
       <c r="I3" t="n">
-        <v>0.63556725980652</v>
+        <v>0.7626807117678239</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1171684914598287</v>
+        <v>-0.1406021897517943</v>
       </c>
     </row>
     <row r="4">
@@ -4680,13 +4680,13 @@
         <v>0.04233103782986536</v>
       </c>
       <c r="H4" t="n">
-        <v>286.8806527439345</v>
+        <v>344.2567832927214</v>
       </c>
       <c r="I4" t="n">
-        <v>538.936434043282</v>
+        <v>646.7237208519382</v>
       </c>
       <c r="J4" t="n">
-        <v>18.72915635788108</v>
+        <v>22.47498762945717</v>
       </c>
     </row>
     <row r="5">
@@ -4724,13 +4724,13 @@
         <v>0.03719769372912385</v>
       </c>
       <c r="H5" t="n">
-        <v>16.32256862005142</v>
+        <v>19.58708234406171</v>
       </c>
       <c r="I5" t="n">
-        <v>32.66886661960218</v>
+        <v>39.20263994352261</v>
       </c>
       <c r="J5" t="n">
-        <v>1.325269777952753</v>
+        <v>1.590323733543314</v>
       </c>
     </row>
     <row r="6">
@@ -4768,13 +4768,13 @@
         <v>0.1333613767685429</v>
       </c>
       <c r="H6" t="n">
-        <v>5.872425577501872</v>
+        <v>7.046910693002239</v>
       </c>
       <c r="I6" t="n">
-        <v>11.76265508118639</v>
+        <v>14.11518609742366</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.002579138217997</v>
+        <v>-2.403094965861602</v>
       </c>
     </row>
     <row r="7">
@@ -4812,13 +4812,13 @@
         <v>0.8335157043083457</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06929810045363163</v>
+        <v>-0.08315772054435734</v>
       </c>
       <c r="I7" t="n">
-        <v>1.457097897994426</v>
+        <v>1.748517477593314</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.199025712429279</v>
+        <v>-1.438830854915136</v>
       </c>
     </row>
     <row r="8">
@@ -4856,13 +4856,13 @@
         <v>0.5727823105937271</v>
       </c>
       <c r="H8" t="n">
-        <v>-523.5590488867367</v>
+        <v>-628.2708586640833</v>
       </c>
       <c r="I8" t="n">
-        <v>1174.945012998747</v>
+        <v>1409.934015598496</v>
       </c>
       <c r="J8" t="n">
-        <v>-1729.074900833013</v>
+        <v>-2074.889880999617</v>
       </c>
     </row>
     <row r="9">
@@ -4900,13 +4900,13 @@
         <v>0.04081584761596257</v>
       </c>
       <c r="H9" t="n">
-        <v>41.40045050907602</v>
+        <v>49.6805406108913</v>
       </c>
       <c r="I9" t="n">
-        <v>100.2728790771937</v>
+        <v>120.3274548926325</v>
       </c>
       <c r="J9" t="n">
-        <v>4.684832708352037</v>
+        <v>5.621799250022473</v>
       </c>
     </row>
     <row r="10">
@@ -4944,13 +4944,13 @@
         <v>0.003160052923044443</v>
       </c>
       <c r="H10" t="n">
-        <v>2.892444901123638</v>
+        <v>3.470933881348371</v>
       </c>
       <c r="I10" t="n">
-        <v>3.827862514767673</v>
+        <v>4.593435017721163</v>
       </c>
       <c r="J10" t="n">
-        <v>1.620635178020765</v>
+        <v>1.944762213624923</v>
       </c>
     </row>
     <row r="11">
@@ -4988,13 +4988,13 @@
         <v>0.3333582434882612</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06172725597362606</v>
+        <v>0.07407270716835131</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2458768182754897</v>
+        <v>0.2950521819305871</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.08711591459161819</v>
+        <v>-0.1045390975099419</v>
       </c>
     </row>
     <row r="12">
@@ -5032,13 +5032,13 @@
         <v>0.5030370130775135</v>
       </c>
       <c r="H12" t="n">
-        <v>33.49520486818356</v>
+        <v>40.19424584182018</v>
       </c>
       <c r="I12" t="n">
-        <v>127.6737925282795</v>
+        <v>153.2085510339356</v>
       </c>
       <c r="J12" t="n">
-        <v>-46.27917928563026</v>
+        <v>-55.53501514275633</v>
       </c>
     </row>
     <row r="13">
@@ -5076,13 +5076,13 @@
         <v>0.00123327446599264</v>
       </c>
       <c r="H13" t="n">
-        <v>34.18060199841231</v>
+        <v>41.01672239809476</v>
       </c>
       <c r="I13" t="n">
-        <v>55.26721613362893</v>
+        <v>66.32065936035454</v>
       </c>
       <c r="J13" t="n">
-        <v>14.98349032555318</v>
+        <v>17.9801883906638</v>
       </c>
     </row>
     <row r="14">
@@ -5120,13 +5120,13 @@
         <v>0.9015386266571279</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.913589487784603</v>
+        <v>-2.296307385341535</v>
       </c>
       <c r="I14" t="n">
-        <v>68.51303472480544</v>
+        <v>82.21564166976651</v>
       </c>
       <c r="J14" t="n">
-        <v>-50.08059668770096</v>
+        <v>-60.09671602524102</v>
       </c>
     </row>
     <row r="15">
@@ -5164,13 +5164,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.215110112480466</v>
+        <v>-1.458132134976557</v>
       </c>
       <c r="I15" t="n">
-        <v>2.048939457389927</v>
+        <v>2.458727348867913</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.15638486597308</v>
+        <v>-12.1876618391677</v>
       </c>
     </row>
     <row r="16">
@@ -5208,13 +5208,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H16" t="n">
-        <v>-964.195873430099</v>
+        <v>-1157.03504811612</v>
       </c>
       <c r="I16" t="n">
-        <v>3335.744209127566</v>
+        <v>4002.893050953082</v>
       </c>
       <c r="J16" t="n">
-        <v>-10988.17387904908</v>
+        <v>-13185.8086548589</v>
       </c>
     </row>
     <row r="17">
@@ -5252,13 +5252,13 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>555.673349685778</v>
+        <v>666.8080196229348</v>
       </c>
       <c r="I17" t="n">
-        <v>555.673349685778</v>
+        <v>666.8080196229348</v>
       </c>
       <c r="J17" t="n">
-        <v>555.673349685778</v>
+        <v>666.8080196229348</v>
       </c>
     </row>
     <row r="18">
@@ -5296,13 +5296,13 @@
         <v>0.6780801094706033</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6682303298796342</v>
+        <v>-0.801876395855551</v>
       </c>
       <c r="I18" t="n">
-        <v>3.787347943597719</v>
+        <v>4.544817532317254</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.218567026021956</v>
+        <v>-6.262280431226346</v>
       </c>
     </row>
     <row r="19">
@@ -5340,13 +5340,13 @@
         <v>0.05775818863725046</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1732668554968047</v>
+        <v>-0.2079202265961669</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01082758148919822</v>
+        <v>0.01299309778703766</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4040181302243796</v>
+        <v>-0.4848217562692553</v>
       </c>
     </row>
     <row r="20">
@@ -5384,13 +5384,13 @@
         <v>0.006133074150475037</v>
       </c>
       <c r="H20" t="n">
-        <v>-72.03623747245938</v>
+        <v>-86.44348496695117</v>
       </c>
       <c r="I20" t="n">
-        <v>-25.97496090966787</v>
+        <v>-31.16995309160146</v>
       </c>
       <c r="J20" t="n">
-        <v>-112.0157692308681</v>
+        <v>-134.4189230770417</v>
       </c>
     </row>
     <row r="21">
@@ -5428,13 +5428,13 @@
         <v>0.02183878958419649</v>
       </c>
       <c r="H21" t="n">
-        <v>25.99238313509477</v>
+        <v>31.19085976211382</v>
       </c>
       <c r="I21" t="n">
-        <v>46.14940333950475</v>
+        <v>55.37928400740564</v>
       </c>
       <c r="J21" t="n">
-        <v>3.792064025611452</v>
+        <v>4.550476830733774</v>
       </c>
     </row>
     <row r="22">
@@ -5472,13 +5472,13 @@
         <v>0.8795727890074994</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0427250022755483</v>
+        <v>0.05127000273065783</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4831209660079663</v>
+        <v>0.5797451592095588</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4083315632703696</v>
+        <v>-0.4899978759244442</v>
       </c>
     </row>
     <row r="23">
@@ -5516,13 +5516,13 @@
         <v>0.7526419827681854</v>
       </c>
       <c r="H23" t="n">
-        <v>0.008912459244297861</v>
+        <v>0.01069495109315745</v>
       </c>
       <c r="I23" t="n">
-        <v>0.04197988271344848</v>
+        <v>0.05037585925613815</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.02588721328826504</v>
+        <v>-0.03106465594591803</v>
       </c>
     </row>
     <row r="24">
@@ -5560,13 +5560,13 @@
         <v>0.6853285557833784</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.19491746047783</v>
+        <v>-1.433900952573385</v>
       </c>
       <c r="I24" t="n">
-        <v>20.9777951455631</v>
+        <v>25.17335417467573</v>
       </c>
       <c r="J24" t="n">
-        <v>-20.73217249808665</v>
+        <v>-24.87860699770398</v>
       </c>
     </row>
     <row r="25">
@@ -5604,13 +5604,13 @@
         <v>0.03182312738649018</v>
       </c>
       <c r="H25" t="n">
-        <v>2.615841701763863</v>
+        <v>3.139010042116635</v>
       </c>
       <c r="I25" t="n">
-        <v>6.992589705686993</v>
+        <v>8.3911076468244</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9273034215007551</v>
+        <v>1.112764105800906</v>
       </c>
     </row>
     <row r="26">
@@ -5648,13 +5648,13 @@
         <v>0.4282542252410364</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2392086276230757</v>
+        <v>0.2870503531476913</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7990390967971372</v>
+        <v>0.9588469161565655</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3462284457145459</v>
+        <v>-0.4154741348574547</v>
       </c>
     </row>
     <row r="27">
@@ -5692,13 +5692,13 @@
         <v>0.06062481656676533</v>
       </c>
       <c r="H27" t="n">
-        <v>0.03044978820684317</v>
+        <v>0.03653974584821185</v>
       </c>
       <c r="I27" t="n">
-        <v>0.07634247226438111</v>
+        <v>0.09161096671725714</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.003102333520029606</v>
+        <v>-0.003722800224035458</v>
       </c>
     </row>
     <row r="28">
@@ -5736,13 +5736,13 @@
         <v>0.1961811327385727</v>
       </c>
       <c r="H28" t="n">
-        <v>10.80331432898135</v>
+        <v>12.96397719477762</v>
       </c>
       <c r="I28" t="n">
-        <v>26.0986795865309</v>
+        <v>31.31841550383708</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.997020028029516</v>
+        <v>-9.596424033635374</v>
       </c>
     </row>
     <row r="29">
@@ -5780,13 +5780,13 @@
         <v>0.002217061581170299</v>
       </c>
       <c r="H29" t="n">
-        <v>8.7597668617708</v>
+        <v>10.51172023412496</v>
       </c>
       <c r="I29" t="n">
-        <v>12.95207424542581</v>
+        <v>15.54248909451099</v>
       </c>
       <c r="J29" t="n">
-        <v>2.802324923644221</v>
+        <v>3.362789908373056</v>
       </c>
     </row>
     <row r="30">
@@ -5824,13 +5824,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.262408473924709</v>
+        <v>-3.914890168709655</v>
       </c>
       <c r="I30" t="n">
-        <v>18.27071551134921</v>
+        <v>21.92485861361903</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.32041230163592</v>
+        <v>-17.1844947619631</v>
       </c>
     </row>
     <row r="31">
@@ -5868,13 +5868,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2583520404840154</v>
+        <v>0.3100224485808187</v>
       </c>
       <c r="I31" t="n">
-        <v>1.23650318207468</v>
+        <v>1.483803818489616</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.632585015705274</v>
+        <v>-0.7591020188463291</v>
       </c>
     </row>
     <row r="32">
@@ -5912,13 +5912,13 @@
         <v>0.1735462217878534</v>
       </c>
       <c r="H32" t="n">
-        <v>364.3594573366452</v>
+        <v>437.2313488039742</v>
       </c>
       <c r="I32" t="n">
-        <v>979.5488477683723</v>
+        <v>1175.458617322047</v>
       </c>
       <c r="J32" t="n">
-        <v>-313.1973623713595</v>
+        <v>-375.836834845632</v>
       </c>
     </row>
     <row r="33">
@@ -5956,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>-11.30694105105372</v>
+        <v>-13.56832926126446</v>
       </c>
       <c r="I33" t="n">
-        <v>189.2070291919078</v>
+        <v>227.0484350302892</v>
       </c>
       <c r="J33" t="n">
-        <v>-155.4488102787125</v>
+        <v>-186.538572334455</v>
       </c>
     </row>
     <row r="34">
@@ -6000,13 +6000,13 @@
         <v>0.9015386266571279</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.04668082333367322</v>
+        <v>-0.05601698800040882</v>
       </c>
       <c r="I34" t="n">
-        <v>3.466768126207668</v>
+        <v>4.160121751449203</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.840165573873293</v>
+        <v>-2.208198688647951</v>
       </c>
     </row>
     <row r="35">
@@ -6044,13 +6044,13 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02065095699026737</v>
+        <v>0.02478114838832083</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1454896561886959</v>
+        <v>0.174587587426435</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1201959250573263</v>
+        <v>-0.1442351100687917</v>
       </c>
     </row>
     <row r="36">
@@ -6088,13 +6088,13 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="H36" t="n">
-        <v>12.59279693352811</v>
+        <v>15.11135632023374</v>
       </c>
       <c r="I36" t="n">
-        <v>72.95946966957641</v>
+        <v>87.55136360349167</v>
       </c>
       <c r="J36" t="n">
-        <v>-60.17729615679767</v>
+        <v>-72.21275538815719</v>
       </c>
     </row>
     <row r="37">
@@ -6132,13 +6132,13 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="H37" t="n">
-        <v>5.848126989281937</v>
+        <v>7.017752387138332</v>
       </c>
       <c r="I37" t="n">
-        <v>46.08866311377883</v>
+        <v>55.30639573653461</v>
       </c>
       <c r="J37" t="n">
-        <v>-28.30059170849562</v>
+        <v>-33.96071005019476</v>
       </c>
     </row>
     <row r="38">
@@ -6176,13 +6176,13 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0008854619062845792</v>
+        <v>0.00106255428754487</v>
       </c>
       <c r="I38" t="n">
-        <v>1.974424764466864</v>
+        <v>2.36930971736024</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.773555301680208</v>
+        <v>-2.128266362016248</v>
       </c>
     </row>
     <row r="39">
@@ -6220,13 +6220,13 @@
         <v>0.6312218204782534</v>
       </c>
       <c r="H39" t="n">
-        <v>0.02304669187336188</v>
+        <v>0.02765603024803442</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07911476672805511</v>
+        <v>0.09493772007366615</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.07048869188474718</v>
+        <v>-0.08458643026169663</v>
       </c>
     </row>
     <row r="40">
@@ -6264,13 +6264,13 @@
         <v>0.5371338571769022</v>
       </c>
       <c r="H40" t="n">
-        <v>8.287851772904538</v>
+        <v>9.945422127485461</v>
       </c>
       <c r="I40" t="n">
-        <v>36.03869491096185</v>
+        <v>43.24643389315406</v>
       </c>
       <c r="J40" t="n">
-        <v>-43.57296046982592</v>
+        <v>-52.28755256379108</v>
       </c>
     </row>
   </sheetData>

--- a/data/annual_loads_stations.xlsx
+++ b/data/annual_loads_stations.xlsx
@@ -499,7 +499,7 @@
         <v>9.61461428113558</v>
       </c>
       <c r="E3" t="n">
-        <v>4294.371840209736</v>
+        <v>6994.710453654764</v>
       </c>
       <c r="F3" t="n">
         <v>624.249353378148</v>
@@ -629,7 +629,7 @@
         <v>8.335676071026965</v>
       </c>
       <c r="E9" t="n">
-        <v>3025.780811905415</v>
+        <v>4844.077617883121</v>
       </c>
       <c r="F9" t="n">
         <v>638.6193178722393</v>
@@ -673,7 +673,7 @@
         <v>28.40103734502056</v>
       </c>
       <c r="E11" t="n">
-        <v>9971.142469072911</v>
+        <v>22012.96040062487</v>
       </c>
       <c r="F11" t="n">
         <v>1210.012386969709</v>
@@ -711,7 +711,7 @@
         <v>2006</v>
       </c>
       <c r="C13" t="n">
-        <v>422.3940769427105</v>
+        <v>484.3160162116932</v>
       </c>
       <c r="D13" t="n">
         <v>22.02788049014049</v>
@@ -783,7 +783,7 @@
         <v>22.30397616371891</v>
       </c>
       <c r="E16" t="n">
-        <v>12225.69550562465</v>
+        <v>15507.08908327438</v>
       </c>
       <c r="F16" t="n">
         <v>1234.296983232236</v>
@@ -849,7 +849,7 @@
         <v>36.99568137853694</v>
       </c>
       <c r="E19" t="n">
-        <v>17077.82296234715</v>
+        <v>24633.70850270884</v>
       </c>
       <c r="F19" t="n">
         <v>2142.501298249766</v>
@@ -937,7 +937,7 @@
         <v>29.69280858301125</v>
       </c>
       <c r="E23" t="n">
-        <v>25936.49615083462</v>
+        <v>28624.34945819745</v>
       </c>
       <c r="F23" t="n">
         <v>937.5051891824171</v>
@@ -956,7 +956,7 @@
         <v>365.2717381410512</v>
       </c>
       <c r="D24" t="n">
-        <v>66.48592828958857</v>
+        <v>172.2663338999198</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1057,8 +1057,12 @@
       <c r="C29" t="n">
         <v>542.2529635820381</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>79.04063887683644</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69040.18945524874</v>
+      </c>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1138,7 +1142,9 @@
         <v>940.5828494911653</v>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>172043.9183464773</v>
+      </c>
       <c r="F33" t="n">
         <v>4870.851457896904</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>574.3310338431747</v>
       </c>
       <c r="D34" t="n">
-        <v>140.5645175956624</v>
+        <v>143.481569403345</v>
       </c>
       <c r="E34" t="n">
         <v>101172.1040152548</v>
@@ -1236,10 +1242,10 @@
         <v>654.1542307852657</v>
       </c>
       <c r="D38" t="n">
-        <v>55.23239112710823</v>
+        <v>64.6691682051284</v>
       </c>
       <c r="E38" t="n">
-        <v>41602.41805519789</v>
+        <v>51551.61014054043</v>
       </c>
       <c r="F38" t="n">
         <v>2877.414839570449</v>
@@ -1258,10 +1264,10 @@
         <v>540.7189704985332</v>
       </c>
       <c r="D39" t="n">
-        <v>80.59472888451928</v>
+        <v>88.02794670191817</v>
       </c>
       <c r="E39" t="n">
-        <v>74870.32089285302</v>
+        <v>89759.28811213108</v>
       </c>
       <c r="F39" t="n">
         <v>2769.542658125109</v>
@@ -1283,7 +1289,7 @@
         <v>86.39708312540093</v>
       </c>
       <c r="E40" t="n">
-        <v>44229.06944246251</v>
+        <v>79388.49168008444</v>
       </c>
       <c r="F40" t="n">
         <v>4516.787915354675</v>
@@ -1321,13 +1327,13 @@
         <v>2016</v>
       </c>
       <c r="C42" t="n">
-        <v>739.0298660417974</v>
+        <v>810.8297248378537</v>
       </c>
       <c r="D42" t="n">
-        <v>57.32612771723028</v>
+        <v>135.1385845571374</v>
       </c>
       <c r="E42" t="n">
-        <v>80676.29224984105</v>
+        <v>118890.0909088559</v>
       </c>
       <c r="F42" t="inlineStr"/>
     </row>
@@ -1344,10 +1350,10 @@
         <v>500.0888686514559</v>
       </c>
       <c r="D43" t="n">
-        <v>30.85328594150314</v>
+        <v>49.29522381273593</v>
       </c>
       <c r="E43" t="n">
-        <v>14140.60468391196</v>
+        <v>23739.94823476762</v>
       </c>
       <c r="F43" t="n">
         <v>3019.684715855197</v>
@@ -1481,7 +1487,9 @@
       <c r="E49" t="n">
         <v>191635.182407868</v>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>7693.93262656047</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1496,10 +1504,10 @@
         <v>747.5116627261049</v>
       </c>
       <c r="D50" t="n">
-        <v>125.8450002230182</v>
+        <v>142.1037232530197</v>
       </c>
       <c r="E50" t="n">
-        <v>99452.51158079253</v>
+        <v>108609.97545837</v>
       </c>
       <c r="F50" t="n">
         <v>5388.319817368871</v>
@@ -1565,7 +1573,7 @@
         <v>5.923668309121244</v>
       </c>
       <c r="E53" t="n">
-        <v>2741.648122159049</v>
+        <v>2828.564435593198</v>
       </c>
       <c r="F53" t="n">
         <v>707.6172625228901</v>
@@ -1584,10 +1592,10 @@
         <v>226.3609882392294</v>
       </c>
       <c r="D54" t="n">
-        <v>11.65675295645575</v>
+        <v>12.19346521545144</v>
       </c>
       <c r="E54" t="n">
-        <v>4908.003722650024</v>
+        <v>5199.694952696468</v>
       </c>
       <c r="F54" t="n">
         <v>1007.593700058762</v>
@@ -1631,7 +1639,7 @@
         <v>20.8977541489777</v>
       </c>
       <c r="E56" t="n">
-        <v>10138.65918563107</v>
+        <v>10439.39329644675</v>
       </c>
       <c r="F56" t="n">
         <v>2126.151506620473</v>
@@ -1873,7 +1881,7 @@
         <v>19.61633942118484</v>
       </c>
       <c r="E67" t="n">
-        <v>9553.036528654606</v>
+        <v>14273.98569047706</v>
       </c>
       <c r="F67" t="n">
         <v>1369.144592361439</v>
@@ -1959,7 +1967,7 @@
         <v>11.58756978807228</v>
       </c>
       <c r="E71" t="n">
-        <v>6013.780186074205</v>
+        <v>6344.764701752276</v>
       </c>
       <c r="F71" t="inlineStr"/>
     </row>
@@ -2084,10 +2092,10 @@
         <v>658.0717263768403</v>
       </c>
       <c r="D77" t="n">
-        <v>140.3089911231126</v>
+        <v>149.0405328869568</v>
       </c>
       <c r="E77" t="n">
-        <v>117368.7966977806</v>
+        <v>125467.5183689415</v>
       </c>
       <c r="F77" t="inlineStr"/>
     </row>
@@ -2104,10 +2112,10 @@
         <v>331.4877721201903</v>
       </c>
       <c r="D78" t="n">
-        <v>34.55298106269688</v>
+        <v>50.18979259735507</v>
       </c>
       <c r="E78" t="n">
-        <v>23244.09741163474</v>
+        <v>44575.50652778852</v>
       </c>
       <c r="F78" t="inlineStr"/>
     </row>
@@ -2127,7 +2135,7 @@
         <v>29.14598483225638</v>
       </c>
       <c r="E79" t="n">
-        <v>22242.37256481489</v>
+        <v>26665.21677702123</v>
       </c>
       <c r="F79" t="inlineStr"/>
     </row>
@@ -2244,7 +2252,7 @@
         <v>370.5516062726167</v>
       </c>
       <c r="D85" t="n">
-        <v>22.90723743495083</v>
+        <v>23.32581395234075</v>
       </c>
       <c r="E85" t="n">
         <v>4967.043752943522</v>
@@ -2269,7 +2277,7 @@
         <v>40.53987019922116</v>
       </c>
       <c r="E86" t="n">
-        <v>4638.379582476791</v>
+        <v>15526.71588886437</v>
       </c>
       <c r="F86" t="inlineStr"/>
     </row>
@@ -2331,7 +2339,7 @@
         <v>12.63927178839586</v>
       </c>
       <c r="E89" t="n">
-        <v>4226.681035363031</v>
+        <v>4460.441339471327</v>
       </c>
       <c r="F89" t="n">
         <v>1044.896885386453</v>
@@ -2527,7 +2535,7 @@
         <v>17.79439531362919</v>
       </c>
       <c r="E98" t="n">
-        <v>4857.854172248018</v>
+        <v>6204.300176263578</v>
       </c>
       <c r="F98" t="n">
         <v>1320.302739733719</v>
@@ -2571,10 +2579,10 @@
         <v>37.23347712024713</v>
       </c>
       <c r="E100" t="n">
-        <v>12662.98955300256</v>
+        <v>17073.01088071766</v>
       </c>
       <c r="F100" t="n">
-        <v>3093.434614512265</v>
+        <v>3114.422018139068</v>
       </c>
     </row>
     <row r="101">
@@ -2593,7 +2601,7 @@
         <v>25.53768851400098</v>
       </c>
       <c r="E101" t="n">
-        <v>5079.111135390028</v>
+        <v>18626.20105913134</v>
       </c>
       <c r="F101" t="n">
         <v>1772.998760300929</v>
@@ -2659,7 +2667,7 @@
         <v>9.483917002062677</v>
       </c>
       <c r="E104" t="n">
-        <v>1533.86967553231</v>
+        <v>1932.576317173651</v>
       </c>
       <c r="F104" t="n">
         <v>1327.408651990087</v>
@@ -2789,7 +2797,7 @@
         <v>13.12749136781718</v>
       </c>
       <c r="E110" t="n">
-        <v>3509.772114256197</v>
+        <v>4949.73144092061</v>
       </c>
       <c r="F110" t="n">
         <v>1819.587265486208</v>
@@ -2975,8 +2983,12 @@
       <c r="C119" t="n">
         <v>25.79900743700395</v>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>4.563323058370141</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3775.021998105326</v>
+      </c>
       <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
@@ -2994,7 +3006,9 @@
       <c r="D120" t="n">
         <v>0.9770348796895605</v>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="n">
+        <v>487.1923265162463</v>
+      </c>
       <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
@@ -3111,7 +3125,7 @@
         <v>2.016574622946294</v>
       </c>
       <c r="E126" t="n">
-        <v>634.6053395558189</v>
+        <v>1602.590247699093</v>
       </c>
       <c r="F126" t="n">
         <v>61.47960654839287</v>
@@ -3152,7 +3166,7 @@
         <v>12.5663757432522</v>
       </c>
       <c r="D128" t="n">
-        <v>1.503870774994698</v>
+        <v>1.630946239459804</v>
       </c>
       <c r="E128" t="n">
         <v>1160.383372960583</v>
@@ -3221,7 +3235,7 @@
         <v>1.454344307776128</v>
       </c>
       <c r="E131" t="n">
-        <v>300.7070578084114</v>
+        <v>1297.381876102844</v>
       </c>
       <c r="F131" t="n">
         <v>76.04592931031137</v>
@@ -3312,7 +3326,7 @@
         <v>516.6387494041873</v>
       </c>
       <c r="F135" t="n">
-        <v>212.2622864804887</v>
+        <v>217.4736289185775</v>
       </c>
     </row>
     <row r="136">
@@ -3325,7 +3339,7 @@
         <v>1996</v>
       </c>
       <c r="C136" t="n">
-        <v>50.79570443575703</v>
+        <v>51.32869255300714</v>
       </c>
       <c r="D136" t="n">
         <v>1.302319497896878</v>
@@ -3413,13 +3427,13 @@
         <v>2000</v>
       </c>
       <c r="C140" t="n">
-        <v>76.17669645769872</v>
+        <v>81.08685298733415</v>
       </c>
       <c r="D140" t="n">
         <v>4.575242451471255</v>
       </c>
       <c r="E140" t="n">
-        <v>1381.698713502394</v>
+        <v>1516.492426408186</v>
       </c>
       <c r="F140" t="n">
         <v>514.5068887583486</v>
@@ -3589,7 +3603,7 @@
         <v>2008</v>
       </c>
       <c r="C148" t="n">
-        <v>65.41108998970012</v>
+        <v>71.08463207595749</v>
       </c>
       <c r="D148" t="n">
         <v>3.262624411887761</v>
@@ -3827,10 +3841,10 @@
         <v>2022</v>
       </c>
       <c r="C159" t="n">
-        <v>38.47147297621791</v>
+        <v>52.97632457821645</v>
       </c>
       <c r="D159" t="n">
-        <v>1.572045305264815</v>
+        <v>2.427926156380575</v>
       </c>
       <c r="E159" t="n">
         <v>342.3730570790243</v>
@@ -3937,7 +3951,7 @@
         <v>2019</v>
       </c>
       <c r="C164" t="n">
-        <v>151.2139403651497</v>
+        <v>137.9310563440462</v>
       </c>
       <c r="D164" t="n">
         <v>3.857625945522277</v>
@@ -3962,10 +3976,10 @@
         <v>134.4611208307123</v>
       </c>
       <c r="D165" t="n">
-        <v>7.137800977493417</v>
+        <v>10.24019644679919</v>
       </c>
       <c r="E165" t="n">
-        <v>2887.3841253616</v>
+        <v>5531.287031060498</v>
       </c>
       <c r="F165" t="n">
         <v>1391.548701768331</v>
@@ -4050,7 +4064,7 @@
         <v>79.31336921214933</v>
       </c>
       <c r="D169" t="n">
-        <v>4.101392902108101</v>
+        <v>4.28544262902544</v>
       </c>
       <c r="E169" t="n">
         <v>3661.801282330153</v>
@@ -4113,7 +4127,7 @@
         <v>2019</v>
       </c>
       <c r="C172" t="n">
-        <v>18.74282453638455</v>
+        <v>18.78688124727843</v>
       </c>
       <c r="D172" t="n">
         <v>0.6178901518620976</v>
@@ -4141,7 +4155,7 @@
         <v>1.309453396994647</v>
       </c>
       <c r="E173" t="n">
-        <v>529.4315191562764</v>
+        <v>749.0986577889029</v>
       </c>
       <c r="F173" t="n">
         <v>313.0517725462432</v>
@@ -4163,7 +4177,7 @@
         <v>0.5422665746753212</v>
       </c>
       <c r="E174" t="n">
-        <v>157.7345632069356</v>
+        <v>214.1688182808587</v>
       </c>
       <c r="F174" t="n">
         <v>165.7129772392721</v>
@@ -4226,13 +4240,13 @@
         <v>14.06433535145543</v>
       </c>
       <c r="D177" t="n">
-        <v>0.5343599965085927</v>
+        <v>0.670718985936172</v>
       </c>
       <c r="E177" t="n">
-        <v>216.0726392431546</v>
+        <v>298.005702836161</v>
       </c>
       <c r="F177" t="n">
-        <v>191.3942954865973</v>
+        <v>195.8554627484408</v>
       </c>
     </row>
     <row r="178">
@@ -4245,7 +4259,7 @@
         <v>2005</v>
       </c>
       <c r="C178" t="n">
-        <v>36.10594259103476</v>
+        <v>40.49770628054306</v>
       </c>
       <c r="D178" t="n">
         <v>1.568285017308244</v>
@@ -4305,13 +4319,13 @@
         <v>2009</v>
       </c>
       <c r="C181" t="n">
-        <v>35.99363165465594</v>
+        <v>40.95647110770329</v>
       </c>
       <c r="D181" t="n">
-        <v>0.9968740664928842</v>
+        <v>1.252879391873128</v>
       </c>
       <c r="E181" t="n">
-        <v>259.3690268560707</v>
+        <v>329.1048795140786</v>
       </c>
       <c r="F181" t="inlineStr"/>
     </row>
@@ -4328,10 +4342,10 @@
         <v>38.9613179373606</v>
       </c>
       <c r="D182" t="n">
-        <v>2.070736213561269</v>
+        <v>2.236296430197122</v>
       </c>
       <c r="E182" t="n">
-        <v>622.4088699275176</v>
+        <v>670.5508169593893</v>
       </c>
       <c r="F182" t="inlineStr"/>
     </row>
@@ -4347,8 +4361,12 @@
       <c r="C183" t="n">
         <v>61.24746583145092</v>
       </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
+      <c r="D183" t="n">
+        <v>5.805716563483374</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1622.063444642838</v>
+      </c>
       <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
@@ -4361,13 +4379,13 @@
         <v>2013</v>
       </c>
       <c r="C184" t="n">
-        <v>40.78136016525453</v>
+        <v>47.91701063717161</v>
       </c>
       <c r="D184" t="n">
         <v>2.515902984650999</v>
       </c>
       <c r="E184" t="n">
-        <v>833.8354119518281</v>
+        <v>889.3250659510968</v>
       </c>
       <c r="F184" t="inlineStr"/>
     </row>
@@ -4481,13 +4499,13 @@
         <v>2019</v>
       </c>
       <c r="C190" t="n">
-        <v>87.5360265012506</v>
+        <v>103.9758223784085</v>
       </c>
       <c r="D190" t="n">
-        <v>2.774667797064762</v>
+        <v>13.14216228483046</v>
       </c>
       <c r="E190" t="n">
-        <v>711.1780694829719</v>
+        <v>1037.211966257285</v>
       </c>
       <c r="F190" t="inlineStr"/>
     </row>
@@ -4595,7 +4613,7 @@
         <v>2.32337679173408</v>
       </c>
       <c r="I2" t="n">
-        <v>6.310218629762883</v>
+        <v>6.289783162135742</v>
       </c>
       <c r="J2" t="n">
         <v>-1.888829134281557</v>
@@ -4673,20 +4691,20 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>increasing</t>
+          <t>no trend</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.04233103782986536</v>
+        <v>0.1019484791528631</v>
       </c>
       <c r="H4" t="n">
-        <v>344.2567832927214</v>
+        <v>284.5510454875292</v>
       </c>
       <c r="I4" t="n">
-        <v>646.7237208519382</v>
+        <v>721.4151579784237</v>
       </c>
       <c r="J4" t="n">
-        <v>22.47498762945717</v>
+        <v>-67.62656264210636</v>
       </c>
     </row>
     <row r="5">
@@ -4765,13 +4783,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.1333613767685429</v>
+        <v>0.1444870405706253</v>
       </c>
       <c r="H6" t="n">
-        <v>7.046910693002239</v>
+        <v>6.933538795261611</v>
       </c>
       <c r="I6" t="n">
-        <v>14.11518609742366</v>
+        <v>14.12147928043259</v>
       </c>
       <c r="J6" t="n">
         <v>-2.403094965861602</v>
@@ -4809,16 +4827,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8335157043083457</v>
+        <v>0.7576397352113808</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08315772054435734</v>
+        <v>-0.0879530879499768</v>
       </c>
       <c r="I7" t="n">
-        <v>1.748517477593314</v>
+        <v>1.826417315597018</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.438830854915136</v>
+        <v>-2.035080448864186</v>
       </c>
     </row>
     <row r="8">
@@ -4853,16 +4871,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.5727823105937271</v>
+        <v>0.6732623633112398</v>
       </c>
       <c r="H8" t="n">
-        <v>-628.2708586640833</v>
+        <v>-725.6994555888059</v>
       </c>
       <c r="I8" t="n">
-        <v>1409.934015598496</v>
+        <v>1726.591554740195</v>
       </c>
       <c r="J8" t="n">
-        <v>-2074.889880999617</v>
+        <v>-2633.27278778162</v>
       </c>
     </row>
     <row r="9">
@@ -4897,16 +4915,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.04081584761596257</v>
+        <v>0.01432574254310803</v>
       </c>
       <c r="H9" t="n">
-        <v>49.6805406108913</v>
+        <v>67.58589623592515</v>
       </c>
       <c r="I9" t="n">
-        <v>120.3274548926325</v>
+        <v>175.6117584630865</v>
       </c>
       <c r="J9" t="n">
-        <v>5.621799250022473</v>
+        <v>12.73374981578935</v>
       </c>
     </row>
     <row r="10">
@@ -5032,13 +5050,13 @@
         <v>0.5030370130775135</v>
       </c>
       <c r="H12" t="n">
-        <v>40.19424584182018</v>
+        <v>43.99227185463047</v>
       </c>
       <c r="I12" t="n">
-        <v>153.2085510339356</v>
+        <v>166.1441637751303</v>
       </c>
       <c r="J12" t="n">
-        <v>-55.53501514275633</v>
+        <v>-57.0336519296224</v>
       </c>
     </row>
     <row r="13">
@@ -5164,13 +5182,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.458132134976557</v>
+        <v>-1.658683993950066</v>
       </c>
       <c r="I15" t="n">
-        <v>2.458727348867913</v>
+        <v>4.17546032446152</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.1876618391677</v>
+        <v>-18.34327310987147</v>
       </c>
     </row>
     <row r="16">
@@ -5208,13 +5226,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H16" t="n">
-        <v>-1157.03504811612</v>
+        <v>-1416.681676954807</v>
       </c>
       <c r="I16" t="n">
-        <v>4002.893050953082</v>
+        <v>3778.08089655529</v>
       </c>
       <c r="J16" t="n">
-        <v>-13185.8086548589</v>
+        <v>-15516.67266450654</v>
       </c>
     </row>
     <row r="17">
@@ -5346,7 +5364,7 @@
         <v>0.01299309778703766</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4848217562692553</v>
+        <v>-0.4864098227719608</v>
       </c>
     </row>
     <row r="20">
@@ -5381,16 +5399,16 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.006133074150475037</v>
+        <v>0.0130971254873018</v>
       </c>
       <c r="H20" t="n">
-        <v>-86.44348496695117</v>
+        <v>-97.31040128260565</v>
       </c>
       <c r="I20" t="n">
-        <v>-31.16995309160146</v>
+        <v>-28.55560601376133</v>
       </c>
       <c r="J20" t="n">
-        <v>-134.4189230770417</v>
+        <v>-153.0466569291263</v>
       </c>
     </row>
     <row r="21">
@@ -5513,16 +5531,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.7526419827681854</v>
+        <v>0.9671423309063722</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01069495109315745</v>
+        <v>-0.001387679920261534</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05037585925613815</v>
+        <v>0.04154665131223973</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.03106465594591803</v>
+        <v>-0.05886731056122541</v>
       </c>
     </row>
     <row r="24">
@@ -5557,16 +5575,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.6853285557833784</v>
+        <v>0.6494456692174662</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.433900952573385</v>
+        <v>-2.822632665609356</v>
       </c>
       <c r="I24" t="n">
-        <v>25.17335417467573</v>
+        <v>27.27245643023724</v>
       </c>
       <c r="J24" t="n">
-        <v>-24.87860699770398</v>
+        <v>-46.03579103678887</v>
       </c>
     </row>
     <row r="25">
@@ -5645,16 +5663,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.4282542252410364</v>
+        <v>0.2783473662511158</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2870503531476913</v>
+        <v>0.3277097710482768</v>
       </c>
       <c r="I26" t="n">
         <v>0.9588469161565655</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4154741348574547</v>
+        <v>-0.3595724311563117</v>
       </c>
     </row>
     <row r="27">
@@ -5685,20 +5703,20 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>no trend</t>
+          <t>increasing</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.06062481656676533</v>
+        <v>0.02712095825238414</v>
       </c>
       <c r="H27" t="n">
-        <v>0.03653974584821185</v>
+        <v>0.04229539519932368</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09161096671725714</v>
+        <v>0.09165931053246608</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.003722800224035458</v>
+        <v>0.005500908742017459</v>
       </c>
     </row>
     <row r="28">
@@ -5742,7 +5760,7 @@
         <v>31.31841550383708</v>
       </c>
       <c r="J28" t="n">
-        <v>-9.596424033635374</v>
+        <v>-9.630482150512398</v>
       </c>
     </row>
     <row r="29">
@@ -5777,10 +5795,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.002217061581170299</v>
+        <v>0.002588571976172904</v>
       </c>
       <c r="H29" t="n">
-        <v>10.51172023412496</v>
+        <v>10.50126200689703</v>
       </c>
       <c r="I29" t="n">
         <v>15.54248909451099</v>
@@ -5824,7 +5842,7 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H30" t="n">
-        <v>-3.914890168709655</v>
+        <v>-3.575836106992045</v>
       </c>
       <c r="I30" t="n">
         <v>21.92485861361903</v>
@@ -5868,13 +5886,13 @@
         <v>0.5361867719001741</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3100224485808187</v>
+        <v>0.323168857646343</v>
       </c>
       <c r="I31" t="n">
-        <v>1.483803818489616</v>
+        <v>1.55368975202154</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.7591020188463291</v>
+        <v>-1.242008439627743</v>
       </c>
     </row>
     <row r="32">
@@ -5909,16 +5927,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.1735462217878534</v>
+        <v>0.5361867719001741</v>
       </c>
       <c r="H32" t="n">
-        <v>437.2313488039742</v>
+        <v>389.935244278312</v>
       </c>
       <c r="I32" t="n">
-        <v>1175.458617322047</v>
+        <v>1532.917694873291</v>
       </c>
       <c r="J32" t="n">
-        <v>-375.836834845632</v>
+        <v>-467.3714371825862</v>
       </c>
     </row>
     <row r="33">
@@ -6041,13 +6059,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.7105230229164894</v>
+        <v>0.2655103889538737</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02478114838832083</v>
+        <v>0.04368852423093159</v>
       </c>
       <c r="I35" t="n">
-        <v>0.174587587426435</v>
+        <v>0.2304256015589452</v>
       </c>
       <c r="J35" t="n">
         <v>-0.1442351100687917</v>
@@ -6085,16 +6103,16 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.7105230229164894</v>
+        <v>0.3864762307712328</v>
       </c>
       <c r="H36" t="n">
-        <v>15.11135632023374</v>
+        <v>27.97194516858735</v>
       </c>
       <c r="I36" t="n">
-        <v>87.55136360349167</v>
+        <v>125.0628069142367</v>
       </c>
       <c r="J36" t="n">
-        <v>-72.21275538815719</v>
+        <v>-79.39285653432115</v>
       </c>
     </row>
     <row r="37">
@@ -6132,10 +6150,10 @@
         <v>0.7105230229164894</v>
       </c>
       <c r="H37" t="n">
-        <v>7.017752387138332</v>
+        <v>8.133044202599189</v>
       </c>
       <c r="I37" t="n">
-        <v>55.30639573653461</v>
+        <v>57.53697936745633</v>
       </c>
       <c r="J37" t="n">
         <v>-33.96071005019476</v>
@@ -6173,16 +6191,16 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0.6693340144640527</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00106255428754487</v>
+        <v>-0.5281429905704358</v>
       </c>
       <c r="I38" t="n">
-        <v>2.36930971736024</v>
+        <v>1.740134882367078</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.128266362016248</v>
+        <v>-2.405590012836732</v>
       </c>
     </row>
     <row r="39">
@@ -6217,16 +6235,16 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.6312218204782534</v>
+        <v>0.6693340144640527</v>
       </c>
       <c r="H39" t="n">
-        <v>0.02765603024803442</v>
+        <v>0.02916914647222391</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09493772007366615</v>
+        <v>0.246610406161959</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.08458643026169663</v>
+        <v>-0.0943439280170939</v>
       </c>
     </row>
     <row r="40">
@@ -6261,16 +6279,16 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.5371338571769022</v>
+        <v>0.5829505577618919</v>
       </c>
       <c r="H40" t="n">
-        <v>9.945422127485461</v>
+        <v>7.828092881049773</v>
       </c>
       <c r="I40" t="n">
-        <v>43.24643389315406</v>
+        <v>55.79478544822852</v>
       </c>
       <c r="J40" t="n">
-        <v>-52.28755256379108</v>
+        <v>-63.79420127294421</v>
       </c>
     </row>
   </sheetData>
